--- a/research/traditional_assets/database/data/iceland/iceland_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_telecom_wireless.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07934004606055552</v>
+        <v>0.0792173659684344</v>
       </c>
       <c r="C2">
-        <v>174.6810985733928</v>
+        <v>173.1456586860508</v>
       </c>
       <c r="D2">
-        <v>168.3910985733928</v>
+        <v>168.6446586860507</v>
       </c>
       <c r="E2">
-        <v>-65.09999999999999</v>
+        <v>-63.31099999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.789</v>
       </c>
       <c r="G2">
         <v>6.29</v>
@@ -1439,28 +1439,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08998669999999998</v>
       </c>
       <c r="N2">
-        <v>20.63333333333333</v>
+        <v>20.54334663333333</v>
       </c>
       <c r="O2">
-        <v>4.126666666666666</v>
+        <v>4.108669326666666</v>
       </c>
       <c r="P2">
-        <v>16.50666666666666</v>
+        <v>16.43467730666666</v>
       </c>
       <c r="Q2">
-        <v>32.80666666666666</v>
+        <v>32.73467730666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07934004606055552</v>
+        <v>0.07961107673579233</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549505</v>
+        <v>0.6413836317121623</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>229.2931436904935</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0792173659684344</v>
+        <v>0.07909468587631328</v>
       </c>
       <c r="C3">
-        <v>173.1456586860508</v>
+        <v>171.6109835622626</v>
       </c>
       <c r="D3">
-        <v>168.6446586860507</v>
+        <v>168.8989835622626</v>
       </c>
       <c r="E3">
-        <v>-63.31099999999999</v>
+        <v>-61.52199999999999</v>
       </c>
       <c r="F3">
-        <v>1.789</v>
+        <v>3.577999999999999</v>
       </c>
       <c r="G3">
         <v>6.29</v>
@@ -1521,28 +1521,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M3">
-        <v>0.08998669999999998</v>
+        <v>0.1799734</v>
       </c>
       <c r="N3">
-        <v>20.54334663333333</v>
+        <v>20.45335993333333</v>
       </c>
       <c r="O3">
-        <v>4.108669326666666</v>
+        <v>4.090671986666666</v>
       </c>
       <c r="P3">
-        <v>16.43467730666666</v>
+        <v>16.36268794666666</v>
       </c>
       <c r="Q3">
-        <v>32.73467730666667</v>
+        <v>32.66268794666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07961107673579233</v>
+        <v>0.07988763864929928</v>
       </c>
       <c r="T3">
-        <v>0.6413836317121623</v>
+        <v>0.6466299090154395</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>229.2931436904935</v>
+        <v>114.6465718452468</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07909468587631328</v>
+        <v>0.07897200578419218</v>
       </c>
       <c r="C4">
-        <v>171.6109835622626</v>
+        <v>170.0770766671631</v>
       </c>
       <c r="D4">
-        <v>168.8989835622626</v>
+        <v>169.1540766671631</v>
       </c>
       <c r="E4">
-        <v>-61.52199999999999</v>
+        <v>-59.733</v>
       </c>
       <c r="F4">
-        <v>3.577999999999999</v>
+        <v>5.366999999999999</v>
       </c>
       <c r="G4">
         <v>6.29</v>
@@ -1603,28 +1603,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M4">
-        <v>0.1799734</v>
+        <v>0.2699600999999999</v>
       </c>
       <c r="N4">
-        <v>20.45335993333333</v>
+        <v>20.36337323333333</v>
       </c>
       <c r="O4">
-        <v>4.090671986666666</v>
+        <v>4.072674646666666</v>
       </c>
       <c r="P4">
-        <v>16.36268794666666</v>
+        <v>16.29069858666666</v>
       </c>
       <c r="Q4">
-        <v>32.66268794666667</v>
+        <v>32.59069858666666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07988763864929928</v>
+        <v>0.08016990287030121</v>
       </c>
       <c r="T4">
-        <v>0.6466299090154395</v>
+        <v>0.6519843569847636</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>114.6465718452468</v>
+        <v>76.43104789683119</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07897200578419218</v>
+        <v>0.07884932569207108</v>
       </c>
       <c r="C5">
-        <v>170.0770766671631</v>
+        <v>168.5439414868525</v>
       </c>
       <c r="D5">
-        <v>169.1540766671631</v>
+        <v>169.4099414868525</v>
       </c>
       <c r="E5">
-        <v>-59.733</v>
+        <v>-57.944</v>
       </c>
       <c r="F5">
-        <v>5.366999999999999</v>
+        <v>7.155999999999999</v>
       </c>
       <c r="G5">
         <v>6.29</v>
@@ -1685,28 +1685,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M5">
-        <v>0.2699600999999999</v>
+        <v>0.3599467999999999</v>
       </c>
       <c r="N5">
-        <v>20.36337323333333</v>
+        <v>20.27338653333333</v>
       </c>
       <c r="O5">
-        <v>4.072674646666666</v>
+        <v>4.054677306666666</v>
       </c>
       <c r="P5">
-        <v>16.29069858666666</v>
+        <v>16.21870922666666</v>
       </c>
       <c r="Q5">
-        <v>32.59069858666666</v>
+        <v>32.51870922666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08016990287030121</v>
+        <v>0.08045804759590737</v>
       </c>
       <c r="T5">
-        <v>0.6519843569847636</v>
+        <v>0.6574503559534489</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.43104789683119</v>
+        <v>57.32328592262338</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07884932569207108</v>
+        <v>0.07872664559994995</v>
       </c>
       <c r="C6">
-        <v>168.5439414868525</v>
+        <v>167.0115815285558</v>
       </c>
       <c r="D6">
-        <v>169.4099414868525</v>
+        <v>169.6665815285558</v>
       </c>
       <c r="E6">
-        <v>-57.944</v>
+        <v>-56.15499999999999</v>
       </c>
       <c r="F6">
-        <v>7.155999999999999</v>
+        <v>8.944999999999999</v>
       </c>
       <c r="G6">
         <v>6.29</v>
@@ -1767,28 +1767,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M6">
-        <v>0.3599467999999999</v>
+        <v>0.4499334999999999</v>
       </c>
       <c r="N6">
-        <v>20.27338653333333</v>
+        <v>20.18339983333333</v>
       </c>
       <c r="O6">
-        <v>4.054677306666666</v>
+        <v>4.036679966666666</v>
       </c>
       <c r="P6">
-        <v>16.21870922666666</v>
+        <v>16.14671986666666</v>
       </c>
       <c r="Q6">
-        <v>32.51870922666667</v>
+        <v>32.44671986666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08045804759590737</v>
+        <v>0.08075225852626311</v>
       </c>
       <c r="T6">
-        <v>0.6574503559534489</v>
+        <v>0.6630314285846326</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.32328592262338</v>
+        <v>45.85862873809871</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07872664559994995</v>
+        <v>0.07860396550782883</v>
       </c>
       <c r="C7">
-        <v>167.0115815285558</v>
+        <v>165.4800003207822</v>
       </c>
       <c r="D7">
-        <v>169.6665815285558</v>
+        <v>169.9240003207822</v>
       </c>
       <c r="E7">
-        <v>-56.15499999999999</v>
+        <v>-54.36599999999999</v>
       </c>
       <c r="F7">
-        <v>8.944999999999999</v>
+        <v>10.734</v>
       </c>
       <c r="G7">
         <v>6.29</v>
@@ -1849,28 +1849,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M7">
-        <v>0.4499334999999999</v>
+        <v>0.5399202</v>
       </c>
       <c r="N7">
-        <v>20.18339983333333</v>
+        <v>20.09341313333333</v>
       </c>
       <c r="O7">
-        <v>4.036679966666666</v>
+        <v>4.018682626666666</v>
       </c>
       <c r="P7">
-        <v>16.14671986666666</v>
+        <v>16.07473050666666</v>
       </c>
       <c r="Q7">
-        <v>32.44671986666667</v>
+        <v>32.37473050666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08075225852626311</v>
+        <v>0.0810527292636477</v>
       </c>
       <c r="T7">
-        <v>0.6630314285846326</v>
+        <v>0.6687312474420118</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.85862873809871</v>
+        <v>38.21552394841558</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07860396550782883</v>
+        <v>0.07848128541570774</v>
       </c>
       <c r="C8">
-        <v>165.4800003207822</v>
+        <v>163.9492014134878</v>
       </c>
       <c r="D8">
-        <v>169.9240003207822</v>
+        <v>170.1822014134878</v>
       </c>
       <c r="E8">
-        <v>-54.366</v>
+        <v>-52.577</v>
       </c>
       <c r="F8">
-        <v>10.734</v>
+        <v>12.523</v>
       </c>
       <c r="G8">
         <v>6.29</v>
@@ -1931,28 +1931,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M8">
-        <v>0.5399201999999999</v>
+        <v>0.6299068999999998</v>
       </c>
       <c r="N8">
-        <v>20.09341313333333</v>
+        <v>20.00342643333333</v>
       </c>
       <c r="O8">
-        <v>4.018682626666666</v>
+        <v>4.000685286666666</v>
       </c>
       <c r="P8">
-        <v>16.07473050666666</v>
+        <v>16.00274114666666</v>
       </c>
       <c r="Q8">
-        <v>32.37473050666667</v>
+        <v>32.30274114666666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0810527292636477</v>
+        <v>0.08135966173732015</v>
       </c>
       <c r="T8">
-        <v>0.6687312474420118</v>
+        <v>0.6745536430490121</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.21552394841559</v>
+        <v>32.75616338435623</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07848128541570773</v>
+        <v>0.07835860532358663</v>
       </c>
       <c r="C9">
-        <v>163.9492014134878</v>
+        <v>162.4191883782381</v>
       </c>
       <c r="D9">
-        <v>170.1822014134878</v>
+        <v>170.4411883782381</v>
       </c>
       <c r="E9">
-        <v>-52.577</v>
+        <v>-50.788</v>
       </c>
       <c r="F9">
-        <v>12.523</v>
+        <v>14.312</v>
       </c>
       <c r="G9">
         <v>6.29</v>
@@ -2013,28 +2013,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M9">
-        <v>0.6299068999999999</v>
+        <v>0.7198935999999998</v>
       </c>
       <c r="N9">
-        <v>20.00342643333333</v>
+        <v>19.91343973333333</v>
       </c>
       <c r="O9">
-        <v>4.000685286666666</v>
+        <v>3.982687946666666</v>
       </c>
       <c r="P9">
-        <v>16.00274114666666</v>
+        <v>15.93075178666667</v>
       </c>
       <c r="Q9">
-        <v>32.30274114666666</v>
+        <v>32.23075178666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08135966173732015</v>
+        <v>0.08167326665607241</v>
       </c>
       <c r="T9">
-        <v>0.6745536430490121</v>
+        <v>0.6805026124735558</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.75616338435621</v>
+        <v>28.66164296131169</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07835860532358663</v>
+        <v>0.07823592523146553</v>
       </c>
       <c r="C10">
-        <v>162.4191883782381</v>
+        <v>160.8899648083728</v>
       </c>
       <c r="D10">
-        <v>170.4411883782381</v>
+        <v>170.7009648083728</v>
       </c>
       <c r="E10">
-        <v>-50.788</v>
+        <v>-48.999</v>
       </c>
       <c r="F10">
-        <v>14.312</v>
+        <v>16.101</v>
       </c>
       <c r="G10">
         <v>6.29</v>
@@ -2095,28 +2095,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M10">
-        <v>0.7198935999999998</v>
+        <v>0.8098802999999999</v>
       </c>
       <c r="N10">
-        <v>19.91343973333333</v>
+        <v>19.82345303333333</v>
       </c>
       <c r="O10">
-        <v>3.982687946666666</v>
+        <v>3.964690606666666</v>
       </c>
       <c r="P10">
-        <v>15.93075178666667</v>
+        <v>15.85876242666666</v>
       </c>
       <c r="Q10">
-        <v>32.23075178666667</v>
+        <v>32.15876242666666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08167326665607241</v>
+        <v>0.08199376399062144</v>
       </c>
       <c r="T10">
-        <v>0.6805026124735558</v>
+        <v>0.6865823284788587</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.66164296131169</v>
+        <v>25.47701596561039</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07823592523146553</v>
+        <v>0.07811324513934441</v>
       </c>
       <c r="C11">
-        <v>160.8899648083728</v>
+        <v>159.3615343191723</v>
       </c>
       <c r="D11">
-        <v>170.7009648083728</v>
+        <v>170.9615343191723</v>
       </c>
       <c r="E11">
-        <v>-48.999</v>
+        <v>-47.20999999999999</v>
       </c>
       <c r="F11">
-        <v>16.101</v>
+        <v>17.89</v>
       </c>
       <c r="G11">
         <v>6.29</v>
@@ -2177,28 +2177,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M11">
-        <v>0.8098802999999999</v>
+        <v>0.8998669999999998</v>
       </c>
       <c r="N11">
-        <v>19.82345303333333</v>
+        <v>19.73346633333333</v>
       </c>
       <c r="O11">
-        <v>3.964690606666666</v>
+        <v>3.946693266666666</v>
       </c>
       <c r="P11">
-        <v>15.85876242666666</v>
+        <v>15.78677306666666</v>
       </c>
       <c r="Q11">
-        <v>32.15876242666666</v>
+        <v>32.08677306666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08199376399062144</v>
+        <v>0.08232138348816045</v>
       </c>
       <c r="T11">
-        <v>0.6865823284788587</v>
+        <v>0.6927971492842794</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.47701596561039</v>
+        <v>22.92931436904935</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07811324513934441</v>
+        <v>0.07799056504722329</v>
       </c>
       <c r="C12">
-        <v>159.3615343191723</v>
+        <v>157.8339005480248</v>
       </c>
       <c r="D12">
-        <v>170.9615343191723</v>
+        <v>171.2229005480249</v>
       </c>
       <c r="E12">
-        <v>-47.20999999999999</v>
+        <v>-45.42099999999999</v>
       </c>
       <c r="F12">
-        <v>17.89</v>
+        <v>19.679</v>
       </c>
       <c r="G12">
         <v>6.29</v>
@@ -2259,28 +2259,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M12">
-        <v>0.8998669999999998</v>
+        <v>0.9898536999999998</v>
       </c>
       <c r="N12">
-        <v>19.73346633333333</v>
+        <v>19.64347963333333</v>
       </c>
       <c r="O12">
-        <v>3.946693266666666</v>
+        <v>3.928695926666666</v>
       </c>
       <c r="P12">
-        <v>15.78677306666666</v>
+        <v>15.71478370666666</v>
       </c>
       <c r="Q12">
-        <v>32.08677306666667</v>
+        <v>32.01478370666666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08232138348816045</v>
+        <v>0.08265636522159921</v>
       </c>
       <c r="T12">
-        <v>0.6927971492842796</v>
+        <v>0.699151628984204</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.92931436904935</v>
+        <v>20.84483124459032</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07799056504722329</v>
+        <v>0.07786788495510218</v>
       </c>
       <c r="C13">
-        <v>157.8339005480248</v>
+        <v>156.3070671545964</v>
       </c>
       <c r="D13">
-        <v>171.2229005480249</v>
+        <v>171.4850671545964</v>
       </c>
       <c r="E13">
-        <v>-45.42099999999999</v>
+        <v>-43.632</v>
       </c>
       <c r="F13">
-        <v>19.679</v>
+        <v>21.468</v>
       </c>
       <c r="G13">
         <v>6.29</v>
@@ -2341,28 +2341,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M13">
-        <v>0.9898536999999998</v>
+        <v>1.0798404</v>
       </c>
       <c r="N13">
-        <v>19.64347963333333</v>
+        <v>19.55349293333333</v>
       </c>
       <c r="O13">
-        <v>3.928695926666666</v>
+        <v>3.910698586666666</v>
       </c>
       <c r="P13">
-        <v>15.71478370666666</v>
+        <v>15.64279434666667</v>
       </c>
       <c r="Q13">
-        <v>32.01478370666666</v>
+        <v>31.94279434666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08265636522159921</v>
+        <v>0.08299896017625248</v>
       </c>
       <c r="T13">
-        <v>0.699151628984204</v>
+        <v>0.7056505286773088</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.84483124459032</v>
+        <v>19.1077619742078</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07786788495510218</v>
+        <v>0.07774520486298107</v>
       </c>
       <c r="C14">
-        <v>156.3070671545964</v>
+        <v>154.7810378210011</v>
       </c>
       <c r="D14">
-        <v>171.4850671545964</v>
+        <v>171.7480378210011</v>
       </c>
       <c r="E14">
-        <v>-43.632</v>
+        <v>-41.843</v>
       </c>
       <c r="F14">
-        <v>21.468</v>
+        <v>23.257</v>
       </c>
       <c r="G14">
         <v>6.29</v>
@@ -2423,28 +2423,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M14">
-        <v>1.0798404</v>
+        <v>1.1698271</v>
       </c>
       <c r="N14">
-        <v>19.55349293333333</v>
+        <v>19.46350623333333</v>
       </c>
       <c r="O14">
-        <v>3.910698586666666</v>
+        <v>3.892701246666666</v>
       </c>
       <c r="P14">
-        <v>15.64279434666667</v>
+        <v>15.57080498666666</v>
       </c>
       <c r="Q14">
-        <v>31.94279434666667</v>
+        <v>31.87080498666666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08299896017625248</v>
+        <v>0.08334943087698973</v>
       </c>
       <c r="T14">
-        <v>0.7056505286773088</v>
+        <v>0.7122988283633583</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.1077619742078</v>
+        <v>17.63793413003796</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07774520486298107</v>
+        <v>0.07762252477085996</v>
       </c>
       <c r="C15">
-        <v>154.7810378210011</v>
+        <v>153.2558162519737</v>
       </c>
       <c r="D15">
-        <v>171.7480378210011</v>
+        <v>172.0118162519737</v>
       </c>
       <c r="E15">
-        <v>-41.843</v>
+        <v>-40.05399999999999</v>
       </c>
       <c r="F15">
-        <v>23.257</v>
+        <v>25.046</v>
       </c>
       <c r="G15">
         <v>6.29</v>
@@ -2505,28 +2505,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M15">
-        <v>1.1698271</v>
+        <v>1.2598138</v>
       </c>
       <c r="N15">
-        <v>19.46350623333333</v>
+        <v>19.37351953333333</v>
       </c>
       <c r="O15">
-        <v>3.892701246666666</v>
+        <v>3.874703906666666</v>
       </c>
       <c r="P15">
-        <v>15.57080498666666</v>
+        <v>15.49881562666666</v>
       </c>
       <c r="Q15">
-        <v>31.87080498666666</v>
+        <v>31.79881562666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08334943087698973</v>
+        <v>0.08370805205913949</v>
       </c>
       <c r="T15">
-        <v>0.7122988283633583</v>
+        <v>0.7191017396700139</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.63793413003796</v>
+        <v>16.37808169217811</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07762252477085996</v>
+        <v>0.07749984467873884</v>
       </c>
       <c r="C16">
-        <v>153.2558162519737</v>
+        <v>151.7314061750434</v>
       </c>
       <c r="D16">
-        <v>172.0118162519737</v>
+        <v>172.2764061750435</v>
       </c>
       <c r="E16">
-        <v>-40.05399999999999</v>
+        <v>-38.26499999999999</v>
       </c>
       <c r="F16">
-        <v>25.046</v>
+        <v>26.835</v>
       </c>
       <c r="G16">
         <v>6.29</v>
@@ -2587,28 +2587,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M16">
-        <v>1.2598138</v>
+        <v>1.3498005</v>
       </c>
       <c r="N16">
-        <v>19.37351953333333</v>
+        <v>19.28353283333333</v>
       </c>
       <c r="O16">
-        <v>3.874703906666666</v>
+        <v>3.856706566666666</v>
       </c>
       <c r="P16">
-        <v>15.49881562666666</v>
+        <v>15.42682626666666</v>
       </c>
       <c r="Q16">
-        <v>31.79881562666667</v>
+        <v>31.72682626666666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08370805205913949</v>
+        <v>0.08407511138675158</v>
       </c>
       <c r="T16">
-        <v>0.7191017396700139</v>
+        <v>0.7260647194780023</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.37808169217811</v>
+        <v>15.28620957936623</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07749984467873884</v>
+        <v>0.07737716458661772</v>
       </c>
       <c r="C17">
-        <v>151.7314061750434</v>
+        <v>150.20781134071</v>
       </c>
       <c r="D17">
-        <v>172.2764061750435</v>
+        <v>172.54181134071</v>
       </c>
       <c r="E17">
-        <v>-38.265</v>
+        <v>-36.476</v>
       </c>
       <c r="F17">
-        <v>26.835</v>
+        <v>28.624</v>
       </c>
       <c r="G17">
         <v>6.29</v>
@@ -2669,28 +2669,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M17">
-        <v>1.3498005</v>
+        <v>1.4397872</v>
       </c>
       <c r="N17">
-        <v>19.28353283333333</v>
+        <v>19.19354613333333</v>
       </c>
       <c r="O17">
-        <v>3.856706566666666</v>
+        <v>3.838709226666666</v>
       </c>
       <c r="P17">
-        <v>15.42682626666666</v>
+        <v>15.35483690666666</v>
       </c>
       <c r="Q17">
-        <v>31.72682626666666</v>
+        <v>31.65483690666666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08407511138675158</v>
+        <v>0.08445091022216397</v>
       </c>
       <c r="T17">
-        <v>0.7260647194780023</v>
+        <v>0.7331934845195144</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.28620957936623</v>
+        <v>14.33082148065584</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07737716458661772</v>
+        <v>0.07725448449449661</v>
       </c>
       <c r="C18">
-        <v>150.20781134071</v>
+        <v>148.6850355226202</v>
       </c>
       <c r="D18">
-        <v>172.54181134071</v>
+        <v>172.8080355226203</v>
       </c>
       <c r="E18">
-        <v>-36.476</v>
+        <v>-34.687</v>
       </c>
       <c r="F18">
-        <v>28.624</v>
+        <v>30.413</v>
       </c>
       <c r="G18">
         <v>6.29</v>
@@ -2751,28 +2751,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M18">
-        <v>1.4397872</v>
+        <v>1.5297739</v>
       </c>
       <c r="N18">
-        <v>19.19354613333333</v>
+        <v>19.10355943333333</v>
       </c>
       <c r="O18">
-        <v>3.838709226666666</v>
+        <v>3.820711886666667</v>
       </c>
       <c r="P18">
-        <v>15.35483690666666</v>
+        <v>15.28284754666666</v>
       </c>
       <c r="Q18">
-        <v>31.65483690666666</v>
+        <v>31.58284754666666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08445091022216397</v>
+        <v>0.08483576445120075</v>
       </c>
       <c r="T18">
-        <v>0.7331934845195144</v>
+        <v>0.7404940270319063</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.33082148065584</v>
+        <v>13.48783198179374</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07725448449449661</v>
+        <v>0.07734780440237551</v>
       </c>
       <c r="C19">
-        <v>148.6850355226202</v>
+        <v>146.6934502541758</v>
       </c>
       <c r="D19">
-        <v>172.8080355226203</v>
+        <v>172.6054502541758</v>
       </c>
       <c r="E19">
-        <v>-34.687</v>
+        <v>-32.898</v>
       </c>
       <c r="F19">
-        <v>30.413</v>
+        <v>32.202</v>
       </c>
       <c r="G19">
         <v>6.29</v>
@@ -2833,45 +2833,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M19">
-        <v>1.5297739</v>
+        <v>1.6680636</v>
       </c>
       <c r="N19">
-        <v>19.10355943333333</v>
+        <v>18.96526973333333</v>
       </c>
       <c r="O19">
-        <v>3.820711886666667</v>
+        <v>3.793053946666666</v>
       </c>
       <c r="P19">
-        <v>15.28284754666666</v>
+        <v>15.17221578666666</v>
       </c>
       <c r="Q19">
-        <v>31.58284754666666</v>
+        <v>31.47221578666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08483576445120075</v>
+        <v>0.08523000536875064</v>
       </c>
       <c r="T19">
-        <v>0.7404940270319063</v>
+        <v>0.7479726315567956</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.48783198179374</v>
+        <v>12.3696322690174</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07734780440237553</v>
+        <v>0.0772371243102544</v>
       </c>
       <c r="C20">
-        <v>146.6934502541758</v>
+        <v>145.1447746759116</v>
       </c>
       <c r="D20">
-        <v>172.6054502541758</v>
+        <v>172.8457746759116</v>
       </c>
       <c r="E20">
-        <v>-32.898</v>
+        <v>-31.109</v>
       </c>
       <c r="F20">
-        <v>32.202</v>
+        <v>33.99099999999999</v>
       </c>
       <c r="G20">
         <v>6.29</v>
@@ -2915,28 +2915,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M20">
-        <v>1.6680636</v>
+        <v>1.7607338</v>
       </c>
       <c r="N20">
-        <v>18.96526973333333</v>
+        <v>18.87259953333333</v>
       </c>
       <c r="O20">
-        <v>3.793053946666666</v>
+        <v>3.774519906666666</v>
       </c>
       <c r="P20">
-        <v>15.17221578666666</v>
+        <v>15.09807962666666</v>
       </c>
       <c r="Q20">
-        <v>31.47221578666667</v>
+        <v>31.39807962666666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08523000536875064</v>
+        <v>0.08563398062994371</v>
       </c>
       <c r="T20">
-        <v>0.7479726315567955</v>
+        <v>0.755635892983534</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.3696322690174</v>
+        <v>11.71859899170069</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0772371243102544</v>
+        <v>0.07712644421813331</v>
       </c>
       <c r="C21">
-        <v>145.1447746759116</v>
+        <v>143.5967692544136</v>
       </c>
       <c r="D21">
-        <v>172.8457746759116</v>
+        <v>173.0867692544136</v>
       </c>
       <c r="E21">
-        <v>-31.109</v>
+        <v>-29.32</v>
       </c>
       <c r="F21">
-        <v>33.99099999999999</v>
+        <v>35.77999999999999</v>
       </c>
       <c r="G21">
         <v>6.29</v>
@@ -2997,28 +2997,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M21">
-        <v>1.7607338</v>
+        <v>1.853404</v>
       </c>
       <c r="N21">
-        <v>18.87259953333333</v>
+        <v>18.77992933333333</v>
       </c>
       <c r="O21">
-        <v>3.774519906666666</v>
+        <v>3.755985866666666</v>
       </c>
       <c r="P21">
-        <v>15.09807962666666</v>
+        <v>15.02394346666666</v>
       </c>
       <c r="Q21">
-        <v>31.39807962666666</v>
+        <v>31.32394346666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08563398062994371</v>
+        <v>0.08604805527266662</v>
       </c>
       <c r="T21">
-        <v>0.755635892983534</v>
+        <v>0.7634907359459406</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.71859899170069</v>
+        <v>11.13266904211566</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07712644421813331</v>
+        <v>0.07701576412601219</v>
       </c>
       <c r="C22">
-        <v>143.5967692544136</v>
+        <v>142.0494367967448</v>
       </c>
       <c r="D22">
-        <v>173.0867692544136</v>
+        <v>173.3284367967448</v>
       </c>
       <c r="E22">
-        <v>-29.32</v>
+        <v>-27.531</v>
       </c>
       <c r="F22">
-        <v>35.77999999999999</v>
+        <v>37.569</v>
       </c>
       <c r="G22">
         <v>6.29</v>
@@ -3079,28 +3079,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M22">
-        <v>1.853404</v>
+        <v>1.9460742</v>
       </c>
       <c r="N22">
-        <v>18.77992933333333</v>
+        <v>18.68725913333333</v>
       </c>
       <c r="O22">
-        <v>3.755985866666666</v>
+        <v>3.737451826666666</v>
       </c>
       <c r="P22">
-        <v>15.02394346666666</v>
+        <v>14.94980730666667</v>
       </c>
       <c r="Q22">
-        <v>31.32394346666666</v>
+        <v>31.24980730666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08604805527266662</v>
+        <v>0.08647261281773694</v>
       </c>
       <c r="T22">
-        <v>0.7634907359459406</v>
+        <v>0.7715444356922059</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.13266904211566</v>
+        <v>10.60254194487206</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07701576412601219</v>
+        <v>0.07690508403389107</v>
       </c>
       <c r="C23">
-        <v>142.0494367967448</v>
+        <v>140.5027801256669</v>
       </c>
       <c r="D23">
-        <v>173.3284367967448</v>
+        <v>173.5707801256669</v>
       </c>
       <c r="E23">
-        <v>-27.531</v>
+        <v>-25.742</v>
       </c>
       <c r="F23">
-        <v>37.569</v>
+        <v>39.358</v>
       </c>
       <c r="G23">
         <v>6.29</v>
@@ -3161,28 +3161,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M23">
-        <v>1.9460742</v>
+        <v>2.0387444</v>
       </c>
       <c r="N23">
-        <v>18.68725913333333</v>
+        <v>18.59458893333333</v>
       </c>
       <c r="O23">
-        <v>3.737451826666666</v>
+        <v>3.718917786666666</v>
       </c>
       <c r="P23">
-        <v>14.94980730666667</v>
+        <v>14.87567114666667</v>
       </c>
       <c r="Q23">
-        <v>31.24980730666667</v>
+        <v>31.17567114666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08647261281773694</v>
+        <v>0.0869080564537065</v>
       </c>
       <c r="T23">
-        <v>0.7715444356922059</v>
+        <v>0.7798046405601702</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.60254194487206</v>
+        <v>10.12060822010515</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07690508403389107</v>
+        <v>0.07710720394176997</v>
       </c>
       <c r="C24">
-        <v>140.5027801256669</v>
+        <v>138.2717315700667</v>
       </c>
       <c r="D24">
-        <v>173.5707801256669</v>
+        <v>173.1287315700667</v>
       </c>
       <c r="E24">
-        <v>-25.742</v>
+        <v>-23.953</v>
       </c>
       <c r="F24">
-        <v>39.358</v>
+        <v>41.147</v>
       </c>
       <c r="G24">
         <v>6.29</v>
@@ -3243,45 +3243,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M24">
-        <v>2.0387444</v>
+        <v>2.2013645</v>
       </c>
       <c r="N24">
-        <v>18.59458893333333</v>
+        <v>18.43196883333333</v>
       </c>
       <c r="O24">
-        <v>3.718917786666666</v>
+        <v>3.686393766666666</v>
       </c>
       <c r="P24">
-        <v>14.87567114666667</v>
+        <v>14.74557506666666</v>
       </c>
       <c r="Q24">
-        <v>31.17567114666667</v>
+        <v>31.04557506666666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0869080564537065</v>
+        <v>0.08735481031398697</v>
       </c>
       <c r="T24">
-        <v>0.7798046405601702</v>
+        <v>0.7882793962039257</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.12060822010515</v>
+        <v>9.372974504373687</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07710720394176997</v>
+        <v>0.07701012384964885</v>
       </c>
       <c r="C25">
-        <v>138.2717315700667</v>
+        <v>136.694770288509</v>
       </c>
       <c r="D25">
-        <v>173.1287315700667</v>
+        <v>173.340770288509</v>
       </c>
       <c r="E25">
-        <v>-23.953</v>
+        <v>-22.16399999999999</v>
       </c>
       <c r="F25">
-        <v>41.147</v>
+        <v>42.936</v>
       </c>
       <c r="G25">
         <v>6.29</v>
@@ -3325,28 +3325,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M25">
-        <v>2.2013645</v>
+        <v>2.297076</v>
       </c>
       <c r="N25">
-        <v>18.43196883333333</v>
+        <v>18.33625733333333</v>
       </c>
       <c r="O25">
-        <v>3.686393766666666</v>
+        <v>3.667251466666666</v>
       </c>
       <c r="P25">
-        <v>14.74557506666666</v>
+        <v>14.66900586666666</v>
       </c>
       <c r="Q25">
-        <v>31.04557506666666</v>
+        <v>30.96900586666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08735481031398697</v>
+        <v>0.08781332085480112</v>
       </c>
       <c r="T25">
-        <v>0.7882793962039257</v>
+        <v>0.7969771717330434</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.372974504373687</v>
+        <v>8.982433900024784</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07701012384964885</v>
+        <v>0.07691304375752774</v>
       </c>
       <c r="C26">
-        <v>136.694770288509</v>
+        <v>135.1183290309857</v>
       </c>
       <c r="D26">
-        <v>173.340770288509</v>
+        <v>173.5533290309857</v>
       </c>
       <c r="E26">
-        <v>-22.164</v>
+        <v>-20.375</v>
       </c>
       <c r="F26">
-        <v>42.93599999999999</v>
+        <v>44.72499999999999</v>
       </c>
       <c r="G26">
         <v>6.29</v>
@@ -3407,28 +3407,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M26">
-        <v>2.297076</v>
+        <v>2.3927875</v>
       </c>
       <c r="N26">
-        <v>18.33625733333333</v>
+        <v>18.24054583333333</v>
       </c>
       <c r="O26">
-        <v>3.667251466666666</v>
+        <v>3.648109166666666</v>
       </c>
       <c r="P26">
-        <v>14.66900586666666</v>
+        <v>14.59243666666666</v>
       </c>
       <c r="Q26">
-        <v>30.96900586666666</v>
+        <v>30.89243666666666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08781332085480112</v>
+        <v>0.08828405834337032</v>
       </c>
       <c r="T26">
-        <v>0.7969771717330433</v>
+        <v>0.8059068879429373</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.982433900024784</v>
+        <v>8.623136544023792</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07691304375752774</v>
+        <v>0.07681596366540662</v>
       </c>
       <c r="C27">
-        <v>135.1183290309857</v>
+        <v>133.5424097128807</v>
       </c>
       <c r="D27">
-        <v>173.5533290309857</v>
+        <v>173.7664097128807</v>
       </c>
       <c r="E27">
-        <v>-20.375</v>
+        <v>-18.586</v>
       </c>
       <c r="F27">
-        <v>44.72499999999999</v>
+        <v>46.514</v>
       </c>
       <c r="G27">
         <v>6.29</v>
@@ -3489,28 +3489,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M27">
-        <v>2.3927875</v>
+        <v>2.488499</v>
       </c>
       <c r="N27">
-        <v>18.24054583333333</v>
+        <v>18.14483433333333</v>
       </c>
       <c r="O27">
-        <v>3.648109166666666</v>
+        <v>3.628966866666666</v>
       </c>
       <c r="P27">
-        <v>14.59243666666666</v>
+        <v>14.51586746666666</v>
       </c>
       <c r="Q27">
-        <v>30.89243666666666</v>
+        <v>30.81586746666666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08828405834337032</v>
+        <v>0.08876751846676571</v>
       </c>
       <c r="T27">
-        <v>0.8059068879429373</v>
+        <v>0.8150779478341799</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.623136544023792</v>
+        <v>8.291477446176724</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07681596366540662</v>
+        <v>0.07671888357328552</v>
       </c>
       <c r="C28">
-        <v>133.5424097128807</v>
+        <v>131.9670142589956</v>
       </c>
       <c r="D28">
-        <v>173.7664097128807</v>
+        <v>173.9800142589956</v>
       </c>
       <c r="E28">
-        <v>-18.586</v>
+        <v>-16.797</v>
       </c>
       <c r="F28">
-        <v>46.514</v>
+        <v>48.303</v>
       </c>
       <c r="G28">
         <v>6.29</v>
@@ -3571,28 +3571,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M28">
-        <v>2.488499</v>
+        <v>2.5842105</v>
       </c>
       <c r="N28">
-        <v>18.14483433333333</v>
+        <v>18.04912283333333</v>
       </c>
       <c r="O28">
-        <v>3.628966866666666</v>
+        <v>3.609824566666666</v>
       </c>
       <c r="P28">
-        <v>14.51586746666666</v>
+        <v>14.43929826666666</v>
       </c>
       <c r="Q28">
-        <v>30.81586746666666</v>
+        <v>30.73929826666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08876751846676571</v>
+        <v>0.08926422407299386</v>
       </c>
       <c r="T28">
-        <v>0.8150779478341799</v>
+        <v>0.824500269640251</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.291477446176724</v>
+        <v>7.984385688910919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07671888357328552</v>
+        <v>0.0766218034811644</v>
       </c>
       <c r="C29">
-        <v>131.9670142589956</v>
+        <v>130.3921446036083</v>
       </c>
       <c r="D29">
-        <v>173.9800142589956</v>
+        <v>174.1941446036083</v>
       </c>
       <c r="E29">
-        <v>-16.797</v>
+        <v>-15.008</v>
       </c>
       <c r="F29">
-        <v>48.303</v>
+        <v>50.092</v>
       </c>
       <c r="G29">
         <v>6.29</v>
@@ -3653,28 +3653,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M29">
-        <v>2.5842105</v>
+        <v>2.679922</v>
       </c>
       <c r="N29">
-        <v>18.04912283333333</v>
+        <v>17.95341133333333</v>
       </c>
       <c r="O29">
-        <v>3.609824566666666</v>
+        <v>3.590682266666666</v>
       </c>
       <c r="P29">
-        <v>14.43929826666666</v>
+        <v>14.36272906666666</v>
       </c>
       <c r="Q29">
-        <v>30.73929826666667</v>
+        <v>30.66272906666666</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08926422407299386</v>
+        <v>0.08977472705717279</v>
       </c>
       <c r="T29">
-        <v>0.824500269640251</v>
+        <v>0.8341843226076018</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.984385688910919</v>
+        <v>7.6992290571641</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0766218034811644</v>
+        <v>0.07671032338904329</v>
       </c>
       <c r="C30">
-        <v>130.3921446036083</v>
+        <v>128.4078743608844</v>
       </c>
       <c r="D30">
-        <v>174.1941446036083</v>
+        <v>173.9988743608844</v>
       </c>
       <c r="E30">
-        <v>-15.008</v>
+        <v>-13.21899999999999</v>
       </c>
       <c r="F30">
-        <v>50.092</v>
+        <v>51.881</v>
       </c>
       <c r="G30">
         <v>6.29</v>
@@ -3735,45 +3735,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M30">
-        <v>2.679922</v>
+        <v>2.8171383</v>
       </c>
       <c r="N30">
-        <v>17.95341133333333</v>
+        <v>17.81619503333333</v>
       </c>
       <c r="O30">
-        <v>3.590682266666666</v>
+        <v>3.563239006666666</v>
       </c>
       <c r="P30">
-        <v>14.36272906666666</v>
+        <v>14.25295602666666</v>
       </c>
       <c r="Q30">
-        <v>30.66272906666666</v>
+        <v>30.55295602666666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08977472705717279</v>
+        <v>0.09029961040710323</v>
       </c>
       <c r="T30">
-        <v>0.8341843226076018</v>
+        <v>0.844141165799385</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.6992290571641</v>
+        <v>7.324217392285401</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07671032338904329</v>
+        <v>0.07661964329692218</v>
       </c>
       <c r="C31">
-        <v>128.4078743608844</v>
+        <v>126.8189153344431</v>
       </c>
       <c r="D31">
-        <v>173.9988743608844</v>
+        <v>174.1989153344431</v>
       </c>
       <c r="E31">
-        <v>-13.219</v>
+        <v>-11.43</v>
       </c>
       <c r="F31">
-        <v>51.88099999999999</v>
+        <v>53.66999999999999</v>
       </c>
       <c r="G31">
         <v>6.29</v>
@@ -3817,28 +3817,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M31">
-        <v>2.8171383</v>
+        <v>2.914281</v>
       </c>
       <c r="N31">
-        <v>17.81619503333333</v>
+        <v>17.71905233333333</v>
       </c>
       <c r="O31">
-        <v>3.563239006666666</v>
+        <v>3.543810466666666</v>
       </c>
       <c r="P31">
-        <v>14.25295602666666</v>
+        <v>14.17524186666666</v>
       </c>
       <c r="Q31">
-        <v>30.55295602666666</v>
+        <v>30.47524186666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09029961040710323</v>
+        <v>0.09083949042417455</v>
       </c>
       <c r="T31">
-        <v>0.844141165799385</v>
+        <v>0.8543824902252194</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.324217392285401</v>
+        <v>7.080076812542555</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07661964329692218</v>
+        <v>0.07652896320480107</v>
       </c>
       <c r="C32">
-        <v>126.8189153344431</v>
+        <v>125.2304167989075</v>
       </c>
       <c r="D32">
-        <v>174.1989153344431</v>
+        <v>174.3994167989075</v>
       </c>
       <c r="E32">
-        <v>-11.43</v>
+        <v>-9.640999999999998</v>
       </c>
       <c r="F32">
-        <v>53.66999999999999</v>
+        <v>55.459</v>
       </c>
       <c r="G32">
         <v>6.29</v>
@@ -3899,28 +3899,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M32">
-        <v>2.914281</v>
+        <v>3.0114237</v>
       </c>
       <c r="N32">
-        <v>17.71905233333333</v>
+        <v>17.62190963333333</v>
       </c>
       <c r="O32">
-        <v>3.543810466666666</v>
+        <v>3.524381926666666</v>
       </c>
       <c r="P32">
-        <v>14.17524186666666</v>
+        <v>14.09752770666666</v>
       </c>
       <c r="Q32">
-        <v>30.47524186666666</v>
+        <v>30.39752770666666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09083949042417455</v>
+        <v>0.09139501913739285</v>
       </c>
       <c r="T32">
-        <v>0.8543824902252194</v>
+        <v>0.864920664634411</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.080076812542555</v>
+        <v>6.851687237944408</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07652896320480107</v>
+        <v>0.07643828311267997</v>
       </c>
       <c r="C33">
-        <v>125.2304167989075</v>
+        <v>123.6423803461732</v>
       </c>
       <c r="D33">
-        <v>174.3994167989075</v>
+        <v>174.6003803461732</v>
       </c>
       <c r="E33">
-        <v>-9.640999999999998</v>
+        <v>-7.852000000000004</v>
       </c>
       <c r="F33">
-        <v>55.459</v>
+        <v>57.24799999999999</v>
       </c>
       <c r="G33">
         <v>6.29</v>
@@ -3981,28 +3981,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M33">
-        <v>3.0114237</v>
+        <v>3.1085664</v>
       </c>
       <c r="N33">
-        <v>17.62190963333333</v>
+        <v>17.52476693333333</v>
       </c>
       <c r="O33">
-        <v>3.524381926666666</v>
+        <v>3.504953386666666</v>
       </c>
       <c r="P33">
-        <v>14.09752770666666</v>
+        <v>14.01981354666666</v>
       </c>
       <c r="Q33">
-        <v>30.39752770666666</v>
+        <v>30.31981354666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09139501913739285</v>
+        <v>0.09196688693041172</v>
       </c>
       <c r="T33">
-        <v>0.864920664634411</v>
+        <v>0.8757687853497554</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.851687237944408</v>
+        <v>6.637572011758646</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07643828311267997</v>
+        <v>0.07634760302055885</v>
       </c>
       <c r="C34">
-        <v>123.6423803461732</v>
+        <v>122.0548075754817</v>
       </c>
       <c r="D34">
-        <v>174.6003803461732</v>
+        <v>174.8018075754817</v>
       </c>
       <c r="E34">
-        <v>-7.852000000000004</v>
+        <v>-6.063000000000002</v>
       </c>
       <c r="F34">
-        <v>57.24799999999999</v>
+        <v>59.03699999999999</v>
       </c>
       <c r="G34">
         <v>6.29</v>
@@ -4063,28 +4063,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M34">
-        <v>3.1085664</v>
+        <v>3.2057091</v>
       </c>
       <c r="N34">
-        <v>17.52476693333333</v>
+        <v>17.42762423333333</v>
       </c>
       <c r="O34">
-        <v>3.504953386666666</v>
+        <v>3.485524846666666</v>
       </c>
       <c r="P34">
-        <v>14.01981354666666</v>
+        <v>13.94209938666666</v>
       </c>
       <c r="Q34">
-        <v>30.31981354666667</v>
+        <v>30.24209938666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09196688693041172</v>
+        <v>0.09255582540381918</v>
       </c>
       <c r="T34">
-        <v>0.8757687853497554</v>
+        <v>0.8869407305640654</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.637572011758646</v>
+        <v>6.436433465947778</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07634760302055885</v>
+        <v>0.07625692292843773</v>
       </c>
       <c r="C35">
-        <v>122.0548075754817</v>
+        <v>120.467700093463</v>
       </c>
       <c r="D35">
-        <v>174.8018075754817</v>
+        <v>175.003700093463</v>
       </c>
       <c r="E35">
-        <v>-6.063000000000002</v>
+        <v>-4.274000000000001</v>
       </c>
       <c r="F35">
-        <v>59.03699999999999</v>
+        <v>60.82599999999999</v>
       </c>
       <c r="G35">
         <v>6.29</v>
@@ -4145,28 +4145,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M35">
-        <v>3.2057091</v>
+        <v>3.3028518</v>
       </c>
       <c r="N35">
-        <v>17.42762423333333</v>
+        <v>17.33048153333333</v>
       </c>
       <c r="O35">
-        <v>3.485524846666666</v>
+        <v>3.466096306666666</v>
       </c>
       <c r="P35">
-        <v>13.94209938666666</v>
+        <v>13.86438522666666</v>
       </c>
       <c r="Q35">
-        <v>30.24209938666667</v>
+        <v>30.16438522666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09255582540381918</v>
+        <v>0.09316261049763294</v>
       </c>
       <c r="T35">
-        <v>0.8869407305640654</v>
+        <v>0.8984512195727483</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.436433465947778</v>
+        <v>6.247126599302256</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07625692292843773</v>
+        <v>0.07644624283631662</v>
       </c>
       <c r="C36">
-        <v>120.467700093463</v>
+        <v>118.2577216125351</v>
       </c>
       <c r="D36">
-        <v>175.003700093463</v>
+        <v>174.5827216125351</v>
       </c>
       <c r="E36">
-        <v>-4.274000000000001</v>
+        <v>-2.484999999999999</v>
       </c>
       <c r="F36">
-        <v>60.82599999999999</v>
+        <v>62.61499999999999</v>
       </c>
       <c r="G36">
         <v>6.29</v>
@@ -4227,45 +4227,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M36">
-        <v>3.3028518</v>
+        <v>3.4626095</v>
       </c>
       <c r="N36">
-        <v>17.33048153333333</v>
+        <v>17.17072383333333</v>
       </c>
       <c r="O36">
-        <v>3.466096306666666</v>
+        <v>3.434144766666666</v>
       </c>
       <c r="P36">
-        <v>13.86438522666666</v>
+        <v>13.73657906666666</v>
       </c>
       <c r="Q36">
-        <v>30.16438522666667</v>
+        <v>30.03657906666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09316261049763294</v>
+        <v>0.09378806590202558</v>
       </c>
       <c r="T36">
-        <v>0.8984512195727483</v>
+        <v>0.9103158774740061</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.247126599302256</v>
+        <v>5.95889699180151</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07644624283631662</v>
+        <v>0.07636356274419551</v>
       </c>
       <c r="C37">
-        <v>118.2577216125351</v>
+        <v>116.6523226289144</v>
       </c>
       <c r="D37">
-        <v>174.5827216125351</v>
+        <v>174.7663226289144</v>
       </c>
       <c r="E37">
-        <v>-2.484999999999999</v>
+        <v>-0.695999999999998</v>
       </c>
       <c r="F37">
-        <v>62.61499999999999</v>
+        <v>64.404</v>
       </c>
       <c r="G37">
         <v>6.29</v>
@@ -4309,28 +4309,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M37">
-        <v>3.4626095</v>
+        <v>3.5615412</v>
       </c>
       <c r="N37">
-        <v>17.17072383333333</v>
+        <v>17.07179213333333</v>
       </c>
       <c r="O37">
-        <v>3.434144766666666</v>
+        <v>3.414358426666666</v>
       </c>
       <c r="P37">
-        <v>13.73657906666666</v>
+        <v>13.65743370666666</v>
       </c>
       <c r="Q37">
-        <v>30.03657906666666</v>
+        <v>29.95743370666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09378806590202558</v>
+        <v>0.0944330667878055</v>
       </c>
       <c r="T37">
-        <v>0.9103158774740061</v>
+        <v>0.9225513059346784</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.95889699180151</v>
+        <v>5.793372075362579</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07636356274419552</v>
+        <v>0.07628088265207442</v>
       </c>
       <c r="C38">
-        <v>116.6523226289143</v>
+        <v>115.0473102221651</v>
       </c>
       <c r="D38">
-        <v>174.7663226289143</v>
+        <v>174.9503102221651</v>
       </c>
       <c r="E38">
-        <v>-0.695999999999998</v>
+        <v>1.093000000000004</v>
       </c>
       <c r="F38">
-        <v>64.404</v>
+        <v>66.193</v>
       </c>
       <c r="G38">
         <v>6.29</v>
@@ -4391,28 +4391,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M38">
-        <v>3.5615412</v>
+        <v>3.6604729</v>
       </c>
       <c r="N38">
-        <v>17.07179213333333</v>
+        <v>16.97286043333333</v>
       </c>
       <c r="O38">
-        <v>3.414358426666666</v>
+        <v>3.394572086666666</v>
       </c>
       <c r="P38">
-        <v>13.65743370666666</v>
+        <v>13.57828834666666</v>
       </c>
       <c r="Q38">
-        <v>29.95743370666666</v>
+        <v>29.87828834666666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0944330667878055</v>
+        <v>0.09509854389218161</v>
       </c>
       <c r="T38">
-        <v>0.9225513059346783</v>
+        <v>0.9351751606956893</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.793372075362579</v>
+        <v>5.636794451704131</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07628088265207442</v>
+        <v>0.0761982025599533</v>
       </c>
       <c r="C39">
-        <v>115.0473102221651</v>
+        <v>113.4426856144961</v>
       </c>
       <c r="D39">
-        <v>174.9503102221651</v>
+        <v>175.134685614496</v>
       </c>
       <c r="E39">
-        <v>1.093000000000004</v>
+        <v>2.881999999999991</v>
       </c>
       <c r="F39">
-        <v>66.193</v>
+        <v>67.98199999999999</v>
       </c>
       <c r="G39">
         <v>6.29</v>
@@ -4473,28 +4473,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M39">
-        <v>3.6604729</v>
+        <v>3.759404599999999</v>
       </c>
       <c r="N39">
-        <v>16.97286043333333</v>
+        <v>16.87392873333333</v>
       </c>
       <c r="O39">
-        <v>3.394572086666666</v>
+        <v>3.374785746666666</v>
       </c>
       <c r="P39">
-        <v>13.57828834666666</v>
+        <v>13.49914298666666</v>
       </c>
       <c r="Q39">
-        <v>29.87828834666666</v>
+        <v>29.79914298666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09509854389218161</v>
+        <v>0.09578548799992467</v>
       </c>
       <c r="T39">
-        <v>0.9351751606956893</v>
+        <v>0.9482062365780229</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.636794451704131</v>
+        <v>5.488457755606654</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0761982025599533</v>
+        <v>0.07611552246783218</v>
       </c>
       <c r="C40">
-        <v>113.4426856144961</v>
+        <v>111.8384500332735</v>
       </c>
       <c r="D40">
-        <v>175.134685614496</v>
+        <v>175.3194500332735</v>
       </c>
       <c r="E40">
-        <v>2.881999999999991</v>
+        <v>4.670999999999992</v>
       </c>
       <c r="F40">
-        <v>67.98199999999999</v>
+        <v>69.77099999999999</v>
       </c>
       <c r="G40">
         <v>6.29</v>
@@ -4555,28 +4555,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M40">
-        <v>3.759404599999999</v>
+        <v>3.858336299999999</v>
       </c>
       <c r="N40">
-        <v>16.87392873333333</v>
+        <v>16.77499703333333</v>
       </c>
       <c r="O40">
-        <v>3.374785746666666</v>
+        <v>3.354999406666666</v>
       </c>
       <c r="P40">
-        <v>13.49914298666666</v>
+        <v>13.41999762666666</v>
       </c>
       <c r="Q40">
-        <v>29.79914298666667</v>
+        <v>29.71999762666666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09578548799992467</v>
+        <v>0.09649495486529866</v>
       </c>
       <c r="T40">
-        <v>0.9482062365780229</v>
+        <v>0.9616645608499417</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.488457755606654</v>
+        <v>5.347728069565457</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07611552246783218</v>
+        <v>0.07603284237571108</v>
       </c>
       <c r="C41">
-        <v>111.8384500332735</v>
+        <v>110.2346047110486</v>
       </c>
       <c r="D41">
-        <v>175.3194500332735</v>
+        <v>175.5046047110486</v>
       </c>
       <c r="E41">
-        <v>4.670999999999992</v>
+        <v>6.459999999999994</v>
       </c>
       <c r="F41">
-        <v>69.77099999999999</v>
+        <v>71.55999999999999</v>
       </c>
       <c r="G41">
         <v>6.29</v>
@@ -4637,28 +4637,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M41">
-        <v>3.858336299999999</v>
+        <v>3.957268</v>
       </c>
       <c r="N41">
-        <v>16.77499703333333</v>
+        <v>16.67606533333333</v>
       </c>
       <c r="O41">
-        <v>3.354999406666666</v>
+        <v>3.335213066666666</v>
       </c>
       <c r="P41">
-        <v>13.41999762666666</v>
+        <v>13.34085226666666</v>
       </c>
       <c r="Q41">
-        <v>29.71999762666666</v>
+        <v>29.64085226666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09649495486529866</v>
+        <v>0.09722807062618513</v>
       </c>
       <c r="T41">
-        <v>0.9616645608499417</v>
+        <v>0.9755714959309242</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.347728069565457</v>
+        <v>5.214034867826322</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07603284237571108</v>
+        <v>0.07595016228358996</v>
       </c>
       <c r="C42">
-        <v>110.2346047110486</v>
+        <v>108.6311508855849</v>
       </c>
       <c r="D42">
-        <v>175.5046047110486</v>
+        <v>175.6901508855849</v>
       </c>
       <c r="E42">
-        <v>6.459999999999994</v>
+        <v>8.248999999999995</v>
       </c>
       <c r="F42">
-        <v>71.55999999999999</v>
+        <v>73.34899999999999</v>
       </c>
       <c r="G42">
         <v>6.29</v>
@@ -4719,28 +4719,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M42">
-        <v>3.957268</v>
+        <v>4.0561997</v>
       </c>
       <c r="N42">
-        <v>16.67606533333333</v>
+        <v>16.57713363333333</v>
       </c>
       <c r="O42">
-        <v>3.335213066666666</v>
+        <v>3.315426726666666</v>
       </c>
       <c r="P42">
-        <v>13.34085226666666</v>
+        <v>13.26170690666666</v>
       </c>
       <c r="Q42">
-        <v>29.64085226666666</v>
+        <v>29.56170690666666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09722807062618513</v>
+        <v>0.09798603776879655</v>
       </c>
       <c r="T42">
-        <v>0.9755714959309242</v>
+        <v>0.9899498525400756</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.214034867826322</v>
+        <v>5.086863285684216</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07595016228358996</v>
+        <v>0.07586748219146885</v>
       </c>
       <c r="C43">
-        <v>108.6311508855849</v>
+        <v>107.0280897998857</v>
       </c>
       <c r="D43">
-        <v>175.6901508855849</v>
+        <v>175.8760897998857</v>
       </c>
       <c r="E43">
-        <v>8.248999999999995</v>
+        <v>10.038</v>
       </c>
       <c r="F43">
-        <v>73.34899999999999</v>
+        <v>75.13799999999999</v>
       </c>
       <c r="G43">
         <v>6.29</v>
@@ -4801,28 +4801,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M43">
-        <v>4.0561997</v>
+        <v>4.155131399999999</v>
       </c>
       <c r="N43">
-        <v>16.57713363333333</v>
+        <v>16.47820193333333</v>
       </c>
       <c r="O43">
-        <v>3.315426726666666</v>
+        <v>3.295640386666666</v>
       </c>
       <c r="P43">
-        <v>13.26170690666666</v>
+        <v>13.18256154666667</v>
       </c>
       <c r="Q43">
-        <v>29.56170690666666</v>
+        <v>29.48256154666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09798603776879655</v>
+        <v>0.09877014170942905</v>
       </c>
       <c r="T43">
-        <v>0.9899498525400756</v>
+        <v>1.004824014549543</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.086863285684216</v>
+        <v>4.965747493167926</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07586748219146885</v>
+        <v>0.07578480209934775</v>
       </c>
       <c r="C44">
-        <v>107.0280897998857</v>
+        <v>105.4254227022221</v>
       </c>
       <c r="D44">
-        <v>175.8760897998857</v>
+        <v>176.0624227022221</v>
       </c>
       <c r="E44">
-        <v>10.038</v>
+        <v>11.827</v>
       </c>
       <c r="F44">
-        <v>75.13799999999999</v>
+        <v>76.92699999999999</v>
       </c>
       <c r="G44">
         <v>6.29</v>
@@ -4883,28 +4883,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M44">
-        <v>4.155131399999999</v>
+        <v>4.2540631</v>
       </c>
       <c r="N44">
-        <v>16.47820193333333</v>
+        <v>16.37927023333333</v>
       </c>
       <c r="O44">
-        <v>3.295640386666666</v>
+        <v>3.275854046666666</v>
       </c>
       <c r="P44">
-        <v>13.18256154666667</v>
+        <v>13.10341618666666</v>
       </c>
       <c r="Q44">
-        <v>29.48256154666667</v>
+        <v>29.40341618666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09877014170942905</v>
+        <v>0.09958175806903113</v>
       </c>
       <c r="T44">
-        <v>1.004824014549542</v>
+        <v>1.020220076980394</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.965747493167926</v>
+        <v>4.85026499332681</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07578480209934775</v>
+        <v>0.07570212200722663</v>
       </c>
       <c r="C45">
-        <v>105.4254227022221</v>
+        <v>103.8231508461605</v>
       </c>
       <c r="D45">
-        <v>176.0624227022221</v>
+        <v>176.2491508461605</v>
       </c>
       <c r="E45">
-        <v>11.827</v>
+        <v>13.616</v>
       </c>
       <c r="F45">
-        <v>76.92699999999999</v>
+        <v>78.71599999999999</v>
       </c>
       <c r="G45">
         <v>6.29</v>
@@ -4965,28 +4965,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M45">
-        <v>4.2540631</v>
+        <v>4.352994799999999</v>
       </c>
       <c r="N45">
-        <v>16.37927023333333</v>
+        <v>16.28033853333333</v>
       </c>
       <c r="O45">
-        <v>3.275854046666666</v>
+        <v>3.256067706666666</v>
       </c>
       <c r="P45">
-        <v>13.10341618666666</v>
+        <v>13.02427082666666</v>
       </c>
       <c r="Q45">
-        <v>29.40341618666666</v>
+        <v>29.32427082666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09958175806903113</v>
+        <v>0.1004223607271904</v>
       </c>
       <c r="T45">
-        <v>1.020220076980394</v>
+        <v>1.036165998783777</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.85026499332681</v>
+        <v>4.740031698023929</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07570212200722663</v>
+        <v>0.07561944191510553</v>
       </c>
       <c r="C46">
-        <v>103.8231508461605</v>
+        <v>102.2212754905913</v>
       </c>
       <c r="D46">
-        <v>176.2491508461605</v>
+        <v>176.4362754905913</v>
       </c>
       <c r="E46">
-        <v>13.616</v>
+        <v>15.405</v>
       </c>
       <c r="F46">
-        <v>78.71599999999999</v>
+        <v>80.505</v>
       </c>
       <c r="G46">
         <v>6.29</v>
@@ -5047,28 +5047,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M46">
-        <v>4.352994799999999</v>
+        <v>4.4519265</v>
       </c>
       <c r="N46">
-        <v>16.28033853333333</v>
+        <v>16.18140683333333</v>
       </c>
       <c r="O46">
-        <v>3.256067706666666</v>
+        <v>3.236281366666666</v>
       </c>
       <c r="P46">
-        <v>13.02427082666666</v>
+        <v>12.94512546666666</v>
       </c>
       <c r="Q46">
-        <v>29.32427082666666</v>
+        <v>29.24512546666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1004223607271904</v>
+        <v>0.1012935307547373</v>
       </c>
       <c r="T46">
-        <v>1.036165998783777</v>
+        <v>1.0526917722891</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.740031698023929</v>
+        <v>4.634697660290064</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07561944191510553</v>
+        <v>0.07553676182298441</v>
       </c>
       <c r="C47">
-        <v>102.2212754905913</v>
+        <v>100.6197978997566</v>
       </c>
       <c r="D47">
-        <v>176.4362754905913</v>
+        <v>176.6237978997566</v>
       </c>
       <c r="E47">
-        <v>15.405</v>
+        <v>17.194</v>
       </c>
       <c r="F47">
-        <v>80.505</v>
+        <v>82.294</v>
       </c>
       <c r="G47">
         <v>6.29</v>
@@ -5129,28 +5129,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M47">
-        <v>4.4519265</v>
+        <v>4.5508582</v>
       </c>
       <c r="N47">
-        <v>16.18140683333333</v>
+        <v>16.08247513333333</v>
       </c>
       <c r="O47">
-        <v>3.236281366666666</v>
+        <v>3.216495026666666</v>
       </c>
       <c r="P47">
-        <v>12.94512546666666</v>
+        <v>12.86598010666666</v>
       </c>
       <c r="Q47">
-        <v>29.24512546666666</v>
+        <v>29.16598010666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1012935307547373</v>
+        <v>0.10219696633886</v>
       </c>
       <c r="T47">
-        <v>1.0526917722891</v>
+        <v>1.069829611479806</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.634697660290064</v>
+        <v>4.533943363327236</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07553676182298441</v>
+        <v>0.07639408173086332</v>
       </c>
       <c r="C48">
-        <v>100.6197978997566</v>
+        <v>96.90550662867324</v>
       </c>
       <c r="D48">
-        <v>176.6237978997566</v>
+        <v>174.6985066286732</v>
       </c>
       <c r="E48">
-        <v>17.194</v>
+        <v>18.983</v>
       </c>
       <c r="F48">
-        <v>82.294</v>
+        <v>84.083</v>
       </c>
       <c r="G48">
         <v>6.29</v>
@@ -5211,45 +5211,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M48">
-        <v>4.5508582</v>
+        <v>4.8599974</v>
       </c>
       <c r="N48">
-        <v>16.08247513333333</v>
+        <v>15.77333593333333</v>
       </c>
       <c r="O48">
-        <v>3.216495026666666</v>
+        <v>3.154667186666666</v>
       </c>
       <c r="P48">
-        <v>12.86598010666666</v>
+        <v>12.61866874666666</v>
       </c>
       <c r="Q48">
-        <v>29.16598010666667</v>
+        <v>28.91866874666666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.10219696633886</v>
+        <v>0.1031344938318176</v>
       </c>
       <c r="T48">
-        <v>1.069829611479806</v>
+        <v>1.087614161583368</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.533943363327236</v>
+        <v>4.245544109413171</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07639408173086332</v>
+        <v>0.07633140163874219</v>
       </c>
       <c r="C49">
-        <v>96.90550662867324</v>
+        <v>95.255844568179</v>
       </c>
       <c r="D49">
-        <v>174.6985066286732</v>
+        <v>174.837844568179</v>
       </c>
       <c r="E49">
-        <v>18.983</v>
+        <v>20.77200000000001</v>
       </c>
       <c r="F49">
-        <v>84.083</v>
+        <v>85.872</v>
       </c>
       <c r="G49">
         <v>6.29</v>
@@ -5293,28 +5293,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M49">
-        <v>4.8599974</v>
+        <v>4.9634016</v>
       </c>
       <c r="N49">
-        <v>15.77333593333333</v>
+        <v>15.66993173333333</v>
       </c>
       <c r="O49">
-        <v>3.154667186666666</v>
+        <v>3.133986346666666</v>
       </c>
       <c r="P49">
-        <v>12.61866874666666</v>
+        <v>12.53594538666666</v>
       </c>
       <c r="Q49">
-        <v>28.91866874666666</v>
+        <v>28.83594538666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1031344938318176</v>
+        <v>0.1041080800745042</v>
       </c>
       <c r="T49">
-        <v>1.087614161583368</v>
+        <v>1.10608273284476</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.245544109413171</v>
+        <v>4.157095273800397</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07633140163874219</v>
+        <v>0.07626872154662107</v>
       </c>
       <c r="C50">
-        <v>95.25584456817901</v>
+        <v>93.60640495445206</v>
       </c>
       <c r="D50">
-        <v>174.837844568179</v>
+        <v>174.9774049544521</v>
       </c>
       <c r="E50">
-        <v>20.77199999999999</v>
+        <v>22.56099999999999</v>
       </c>
       <c r="F50">
-        <v>85.87199999999999</v>
+        <v>87.66099999999999</v>
       </c>
       <c r="G50">
         <v>6.29</v>
@@ -5375,28 +5375,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M50">
-        <v>4.963401599999999</v>
+        <v>5.0668058</v>
       </c>
       <c r="N50">
-        <v>15.66993173333333</v>
+        <v>15.56652753333333</v>
       </c>
       <c r="O50">
-        <v>3.133986346666666</v>
+        <v>3.113305506666666</v>
       </c>
       <c r="P50">
-        <v>12.53594538666666</v>
+        <v>12.45322202666666</v>
       </c>
       <c r="Q50">
-        <v>28.83594538666667</v>
+        <v>28.75322202666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1041080800745042</v>
+        <v>0.1051198461698452</v>
       </c>
       <c r="T50">
-        <v>1.10608273284476</v>
+        <v>1.125275561802677</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.157095273800397</v>
+        <v>4.072256594743246</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07626872154662107</v>
+        <v>0.07760604145449997</v>
       </c>
       <c r="C51">
-        <v>93.60640495445206</v>
+        <v>88.88731932186511</v>
       </c>
       <c r="D51">
-        <v>174.9774049544521</v>
+        <v>172.0473193218651</v>
       </c>
       <c r="E51">
-        <v>22.56099999999999</v>
+        <v>24.34999999999999</v>
       </c>
       <c r="F51">
-        <v>87.66099999999999</v>
+        <v>89.44999999999999</v>
       </c>
       <c r="G51">
         <v>6.29</v>
@@ -5457,45 +5457,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M51">
-        <v>5.0668058</v>
+        <v>5.483285</v>
       </c>
       <c r="N51">
-        <v>15.56652753333333</v>
+        <v>15.15004833333333</v>
       </c>
       <c r="O51">
-        <v>3.113305506666666</v>
+        <v>3.030009666666666</v>
       </c>
       <c r="P51">
-        <v>12.45322202666666</v>
+        <v>12.12003866666666</v>
       </c>
       <c r="Q51">
-        <v>28.75322202666666</v>
+        <v>28.42003866666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1051198461698452</v>
+        <v>0.1061720829089999</v>
       </c>
       <c r="T51">
-        <v>1.125275561802677</v>
+        <v>1.145236103918911</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.072256594743246</v>
+        <v>3.762951102000595</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07760604145449997</v>
+        <v>0.07757136136237885</v>
       </c>
       <c r="C52">
-        <v>88.88731932186511</v>
+        <v>87.17306392139689</v>
       </c>
       <c r="D52">
-        <v>172.0473193218651</v>
+        <v>172.1220639213969</v>
       </c>
       <c r="E52">
-        <v>24.34999999999999</v>
+        <v>26.139</v>
       </c>
       <c r="F52">
-        <v>89.44999999999999</v>
+        <v>91.23899999999999</v>
       </c>
       <c r="G52">
         <v>6.29</v>
@@ -5539,28 +5539,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M52">
-        <v>5.483285</v>
+        <v>5.592950699999999</v>
       </c>
       <c r="N52">
-        <v>15.15004833333333</v>
+        <v>15.04038263333333</v>
       </c>
       <c r="O52">
-        <v>3.030009666666666</v>
+        <v>3.008076526666666</v>
       </c>
       <c r="P52">
-        <v>12.12003866666666</v>
+        <v>12.03230610666666</v>
       </c>
       <c r="Q52">
-        <v>28.42003866666666</v>
+        <v>28.33230610666666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1061720829089999</v>
+        <v>0.1072672680864875</v>
       </c>
       <c r="T52">
-        <v>1.145236103918911</v>
+        <v>1.166011362039889</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.762951102000595</v>
+        <v>3.689167747059407</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07757136136237885</v>
+        <v>0.07753668127025774</v>
       </c>
       <c r="C53">
-        <v>87.17306392139689</v>
+        <v>85.45887349355783</v>
       </c>
       <c r="D53">
-        <v>172.1220639213969</v>
+        <v>172.1968734935578</v>
       </c>
       <c r="E53">
-        <v>26.139</v>
+        <v>27.928</v>
       </c>
       <c r="F53">
-        <v>91.23899999999999</v>
+        <v>93.02799999999999</v>
       </c>
       <c r="G53">
         <v>6.29</v>
@@ -5621,28 +5621,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M53">
-        <v>5.592950699999999</v>
+        <v>5.702616399999999</v>
       </c>
       <c r="N53">
-        <v>15.04038263333333</v>
+        <v>14.93071693333333</v>
       </c>
       <c r="O53">
-        <v>3.008076526666666</v>
+        <v>2.986143386666666</v>
       </c>
       <c r="P53">
-        <v>12.03230610666666</v>
+        <v>11.94457354666666</v>
       </c>
       <c r="Q53">
-        <v>28.33230610666666</v>
+        <v>28.24457354666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1072672680864875</v>
+        <v>0.1084080859797036</v>
       </c>
       <c r="T53">
-        <v>1.166011362039889</v>
+        <v>1.187652255915908</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.689167747059407</v>
+        <v>3.61822221346211</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07753668127025774</v>
+        <v>0.07750200117813663</v>
       </c>
       <c r="C54">
-        <v>85.45887349355783</v>
+        <v>83.74474812310204</v>
       </c>
       <c r="D54">
-        <v>172.1968734935578</v>
+        <v>172.271748123102</v>
       </c>
       <c r="E54">
-        <v>27.928</v>
+        <v>29.717</v>
       </c>
       <c r="F54">
-        <v>93.02799999999999</v>
+        <v>94.81699999999999</v>
       </c>
       <c r="G54">
         <v>6.29</v>
@@ -5703,28 +5703,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M54">
-        <v>5.702616399999999</v>
+        <v>5.8122821</v>
       </c>
       <c r="N54">
-        <v>14.93071693333333</v>
+        <v>14.82105123333333</v>
       </c>
       <c r="O54">
-        <v>2.986143386666666</v>
+        <v>2.964210246666666</v>
       </c>
       <c r="P54">
-        <v>11.94457354666666</v>
+        <v>11.85684098666666</v>
       </c>
       <c r="Q54">
-        <v>28.24457354666666</v>
+        <v>28.15684098666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1084080859797036</v>
+        <v>0.1095974493151843</v>
       </c>
       <c r="T54">
-        <v>1.187652255915908</v>
+        <v>1.210214038893034</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.61822221346211</v>
+        <v>3.549953869811882</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07750200117813663</v>
+        <v>0.07867692108601554</v>
       </c>
       <c r="C55">
-        <v>83.74474812310204</v>
+        <v>79.45482408046303</v>
       </c>
       <c r="D55">
-        <v>172.271748123102</v>
+        <v>169.770824080463</v>
       </c>
       <c r="E55">
-        <v>29.717</v>
+        <v>31.506</v>
       </c>
       <c r="F55">
-        <v>94.81699999999999</v>
+        <v>96.60599999999999</v>
       </c>
       <c r="G55">
         <v>6.29</v>
@@ -5785,45 +5785,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M55">
-        <v>5.8122821</v>
+        <v>6.1924446</v>
       </c>
       <c r="N55">
-        <v>14.82105123333333</v>
+        <v>14.44088873333333</v>
       </c>
       <c r="O55">
-        <v>2.964210246666666</v>
+        <v>2.888177746666666</v>
       </c>
       <c r="P55">
-        <v>11.85684098666666</v>
+        <v>11.55271098666666</v>
       </c>
       <c r="Q55">
-        <v>28.15684098666667</v>
+        <v>27.85271098666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1095974493151843</v>
+        <v>0.1108385241000338</v>
       </c>
       <c r="T55">
-        <v>1.210214038893034</v>
+        <v>1.233756768956122</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.549953869811882</v>
+        <v>3.332017428679674</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07867692108601554</v>
+        <v>0.07866464099389442</v>
       </c>
       <c r="C56">
-        <v>79.45482408046303</v>
+        <v>77.69158781179623</v>
       </c>
       <c r="D56">
-        <v>169.770824080463</v>
+        <v>169.7965878117962</v>
       </c>
       <c r="E56">
-        <v>31.506</v>
+        <v>33.295</v>
       </c>
       <c r="F56">
-        <v>96.60599999999999</v>
+        <v>98.395</v>
       </c>
       <c r="G56">
         <v>6.29</v>
@@ -5867,28 +5867,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M56">
-        <v>6.1924446</v>
+        <v>6.3071195</v>
       </c>
       <c r="N56">
-        <v>14.44088873333333</v>
+        <v>14.32621383333333</v>
       </c>
       <c r="O56">
-        <v>2.888177746666666</v>
+        <v>2.865242766666666</v>
       </c>
       <c r="P56">
-        <v>11.55271098666666</v>
+        <v>11.46097106666666</v>
       </c>
       <c r="Q56">
-        <v>27.85271098666666</v>
+        <v>27.76097106666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1108385241000338</v>
+        <v>0.1121347577642098</v>
       </c>
       <c r="T56">
-        <v>1.233756768956122</v>
+        <v>1.258345842577569</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.332017428679674</v>
+        <v>3.27143529361277</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07866464099389442</v>
+        <v>0.0786523609017733</v>
       </c>
       <c r="C57">
-        <v>77.69158781179623</v>
+        <v>75.92835936391492</v>
       </c>
       <c r="D57">
-        <v>169.7965878117962</v>
+        <v>169.8223593639149</v>
       </c>
       <c r="E57">
-        <v>33.295</v>
+        <v>35.084</v>
       </c>
       <c r="F57">
-        <v>98.395</v>
+        <v>100.184</v>
       </c>
       <c r="G57">
         <v>6.29</v>
@@ -5949,28 +5949,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M57">
-        <v>6.3071195</v>
+        <v>6.4217944</v>
       </c>
       <c r="N57">
-        <v>14.32621383333333</v>
+        <v>14.21153893333333</v>
       </c>
       <c r="O57">
-        <v>2.865242766666666</v>
+        <v>2.842307786666666</v>
       </c>
       <c r="P57">
-        <v>11.46097106666666</v>
+        <v>11.36923114666666</v>
       </c>
       <c r="Q57">
-        <v>27.76097106666666</v>
+        <v>27.66923114666666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1121347577642098</v>
+        <v>0.1134899111403939</v>
       </c>
       <c r="T57">
-        <v>1.258345842577569</v>
+        <v>1.284052601363628</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.27143529361277</v>
+        <v>3.213016806226828</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0786523609017733</v>
+        <v>0.07864008080965218</v>
       </c>
       <c r="C58">
-        <v>75.92835936391492</v>
+        <v>74.16513874038073</v>
       </c>
       <c r="D58">
-        <v>169.8223593639149</v>
+        <v>169.8481387403807</v>
       </c>
       <c r="E58">
-        <v>35.084</v>
+        <v>36.873</v>
       </c>
       <c r="F58">
-        <v>100.184</v>
+        <v>101.973</v>
       </c>
       <c r="G58">
         <v>6.29</v>
@@ -6031,28 +6031,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M58">
-        <v>6.4217944</v>
+        <v>6.5364693</v>
       </c>
       <c r="N58">
-        <v>14.21153893333333</v>
+        <v>14.09686403333333</v>
       </c>
       <c r="O58">
-        <v>2.842307786666666</v>
+        <v>2.819372806666666</v>
       </c>
       <c r="P58">
-        <v>11.36923114666666</v>
+        <v>11.27749122666666</v>
       </c>
       <c r="Q58">
-        <v>27.66923114666666</v>
+        <v>27.57749122666667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1134899111403939</v>
+        <v>0.1149080949061679</v>
       </c>
       <c r="T58">
-        <v>1.284052601363628</v>
+        <v>1.310955023349038</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.213016806226828</v>
+        <v>3.156648090328112</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07864008080965218</v>
+        <v>0.07862780071753109</v>
       </c>
       <c r="C59">
-        <v>74.16513874038073</v>
+        <v>72.40192594475741</v>
       </c>
       <c r="D59">
-        <v>169.8481387403807</v>
+        <v>169.8739259447574</v>
       </c>
       <c r="E59">
-        <v>36.873</v>
+        <v>38.66200000000001</v>
       </c>
       <c r="F59">
-        <v>101.973</v>
+        <v>103.762</v>
       </c>
       <c r="G59">
         <v>6.29</v>
@@ -6113,28 +6113,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M59">
-        <v>6.5364693</v>
+        <v>6.6511442</v>
       </c>
       <c r="N59">
-        <v>14.09686403333333</v>
+        <v>13.98218913333333</v>
       </c>
       <c r="O59">
-        <v>2.819372806666666</v>
+        <v>2.796437826666666</v>
       </c>
       <c r="P59">
-        <v>11.27749122666666</v>
+        <v>11.18575130666666</v>
       </c>
       <c r="Q59">
-        <v>27.57749122666667</v>
+        <v>27.48575130666666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1149080949061679</v>
+        <v>0.1163938112322169</v>
       </c>
       <c r="T59">
-        <v>1.310955023349038</v>
+        <v>1.339138513048039</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.156648090328112</v>
+        <v>3.102223123253489</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07862780071753109</v>
+        <v>0.07861552062540997</v>
       </c>
       <c r="C60">
-        <v>72.40192594475742</v>
+        <v>70.63872098061103</v>
       </c>
       <c r="D60">
-        <v>169.8739259447574</v>
+        <v>169.899720980611</v>
       </c>
       <c r="E60">
-        <v>38.66199999999999</v>
+        <v>40.45099999999999</v>
       </c>
       <c r="F60">
-        <v>103.762</v>
+        <v>105.551</v>
       </c>
       <c r="G60">
         <v>6.29</v>
@@ -6195,28 +6195,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M60">
-        <v>6.651144199999999</v>
+        <v>6.7658191</v>
       </c>
       <c r="N60">
-        <v>13.98218913333333</v>
+        <v>13.86751423333333</v>
       </c>
       <c r="O60">
-        <v>2.796437826666666</v>
+        <v>2.773502846666666</v>
       </c>
       <c r="P60">
-        <v>11.18575130666666</v>
+        <v>11.09401138666666</v>
       </c>
       <c r="Q60">
-        <v>27.48575130666666</v>
+        <v>27.39401138666666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1163938112322168</v>
+        <v>0.1179520015253901</v>
       </c>
       <c r="T60">
-        <v>1.339138513048038</v>
+        <v>1.368696807122601</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.10222312325349</v>
+        <v>3.049643070316989</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07861552062540997</v>
+        <v>0.08234724053328886</v>
       </c>
       <c r="C61">
-        <v>70.63872098061103</v>
+        <v>61.35564738628243</v>
       </c>
       <c r="D61">
-        <v>169.899720980611</v>
+        <v>162.4056473862824</v>
       </c>
       <c r="E61">
-        <v>40.45099999999999</v>
+        <v>42.23999999999999</v>
       </c>
       <c r="F61">
-        <v>105.551</v>
+        <v>107.34</v>
       </c>
       <c r="G61">
         <v>6.29</v>
@@ -6277,45 +6277,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M61">
-        <v>6.7658191</v>
+        <v>7.717746</v>
       </c>
       <c r="N61">
-        <v>13.86751423333333</v>
+        <v>12.91558733333333</v>
       </c>
       <c r="O61">
-        <v>2.773502846666666</v>
+        <v>2.583117466666666</v>
       </c>
       <c r="P61">
-        <v>11.09401138666666</v>
+        <v>10.33246986666666</v>
       </c>
       <c r="Q61">
-        <v>27.39401138666666</v>
+        <v>26.63246986666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1179520015253901</v>
+        <v>0.1195881013332221</v>
       </c>
       <c r="T61">
-        <v>1.368696807122601</v>
+        <v>1.399733015900891</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.049643070316989</v>
+        <v>2.673492148268851</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08234724053328886</v>
+        <v>0.08239736044116774</v>
       </c>
       <c r="C62">
-        <v>61.35564738628243</v>
+        <v>59.47049270490672</v>
       </c>
       <c r="D62">
-        <v>162.4056473862824</v>
+        <v>162.3094927049067</v>
       </c>
       <c r="E62">
-        <v>42.23999999999999</v>
+        <v>44.029</v>
       </c>
       <c r="F62">
-        <v>107.34</v>
+        <v>109.129</v>
       </c>
       <c r="G62">
         <v>6.29</v>
@@ -6359,28 +6359,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M62">
-        <v>7.717746</v>
+        <v>7.8463751</v>
       </c>
       <c r="N62">
-        <v>12.91558733333333</v>
+        <v>12.78695823333333</v>
       </c>
       <c r="O62">
-        <v>2.583117466666666</v>
+        <v>2.557391646666666</v>
       </c>
       <c r="P62">
-        <v>10.33246986666666</v>
+        <v>10.22956658666666</v>
       </c>
       <c r="Q62">
-        <v>26.63246986666666</v>
+        <v>26.52956658666666</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1195881013332221</v>
+        <v>0.1213081036953019</v>
       </c>
       <c r="T62">
-        <v>1.399733015900891</v>
+        <v>1.43236082512935</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.673492148268851</v>
+        <v>2.629664408133296</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08239736044116774</v>
+        <v>0.08244748034904664</v>
       </c>
       <c r="C63">
-        <v>59.47049270490672</v>
+        <v>57.58545181577985</v>
       </c>
       <c r="D63">
-        <v>162.3094927049067</v>
+        <v>162.2134518157798</v>
       </c>
       <c r="E63">
-        <v>44.029</v>
+        <v>45.818</v>
       </c>
       <c r="F63">
-        <v>109.129</v>
+        <v>110.918</v>
       </c>
       <c r="G63">
         <v>6.29</v>
@@ -6441,28 +6441,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M63">
-        <v>7.8463751</v>
+        <v>7.9750042</v>
       </c>
       <c r="N63">
-        <v>12.78695823333333</v>
+        <v>12.65832913333333</v>
       </c>
       <c r="O63">
-        <v>2.557391646666666</v>
+        <v>2.531665826666666</v>
       </c>
       <c r="P63">
-        <v>10.22956658666666</v>
+        <v>10.12666330666666</v>
       </c>
       <c r="Q63">
-        <v>26.52956658666666</v>
+        <v>26.42666330666666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1213081036953019</v>
+        <v>0.1231186324974911</v>
       </c>
       <c r="T63">
-        <v>1.43236082512935</v>
+        <v>1.466705887475096</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.629664408133296</v>
+        <v>2.58725046606663</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08244748034904664</v>
+        <v>0.08249760025692553</v>
       </c>
       <c r="C64">
-        <v>57.58545181577985</v>
+        <v>55.70052451702374</v>
       </c>
       <c r="D64">
-        <v>162.2134518157798</v>
+        <v>162.1175245170237</v>
       </c>
       <c r="E64">
-        <v>45.818</v>
+        <v>47.60699999999999</v>
       </c>
       <c r="F64">
-        <v>110.918</v>
+        <v>112.707</v>
       </c>
       <c r="G64">
         <v>6.29</v>
@@ -6523,28 +6523,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M64">
-        <v>7.9750042</v>
+        <v>8.103633299999998</v>
       </c>
       <c r="N64">
-        <v>12.65832913333333</v>
+        <v>12.52970003333333</v>
       </c>
       <c r="O64">
-        <v>2.531665826666666</v>
+        <v>2.505940006666666</v>
       </c>
       <c r="P64">
-        <v>10.12666330666666</v>
+        <v>10.02376002666666</v>
       </c>
       <c r="Q64">
-        <v>26.42666330666666</v>
+        <v>26.32376002666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1231186324974911</v>
+        <v>0.1250270277214203</v>
       </c>
       <c r="T64">
-        <v>1.466705887475096</v>
+        <v>1.50290743967737</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.58725046606663</v>
+        <v>2.546182998351287</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08249760025692553</v>
+        <v>0.08254772016480441</v>
       </c>
       <c r="C65">
-        <v>55.70052451702374</v>
+        <v>53.81571060723746</v>
       </c>
       <c r="D65">
-        <v>162.1175245170237</v>
+        <v>162.0217106072375</v>
       </c>
       <c r="E65">
-        <v>47.60699999999999</v>
+        <v>49.39599999999999</v>
       </c>
       <c r="F65">
-        <v>112.707</v>
+        <v>114.496</v>
       </c>
       <c r="G65">
         <v>6.29</v>
@@ -6605,28 +6605,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M65">
-        <v>8.103633299999998</v>
+        <v>8.2322624</v>
       </c>
       <c r="N65">
-        <v>12.52970003333333</v>
+        <v>12.40107093333333</v>
       </c>
       <c r="O65">
-        <v>2.505940006666666</v>
+        <v>2.480214186666666</v>
       </c>
       <c r="P65">
-        <v>10.02376002666666</v>
+        <v>9.920856746666663</v>
       </c>
       <c r="Q65">
-        <v>26.32376002666667</v>
+        <v>26.22085674666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1250270277214203</v>
+        <v>0.1270414449022345</v>
       </c>
       <c r="T65">
-        <v>1.50290743967737</v>
+        <v>1.541120189224214</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.546182998351287</v>
+        <v>2.506398889002048</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08254772016480441</v>
+        <v>0.08462584007268331</v>
       </c>
       <c r="C66">
-        <v>53.81571060723746</v>
+        <v>48.15129782698715</v>
       </c>
       <c r="D66">
-        <v>162.0217106072375</v>
+        <v>158.1462978269871</v>
       </c>
       <c r="E66">
-        <v>49.39599999999999</v>
+        <v>51.18499999999999</v>
       </c>
       <c r="F66">
-        <v>114.496</v>
+        <v>116.285</v>
       </c>
       <c r="G66">
         <v>6.29</v>
@@ -6687,45 +6687,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M66">
-        <v>8.2322624</v>
+        <v>8.814402999999999</v>
       </c>
       <c r="N66">
-        <v>12.40107093333333</v>
+        <v>11.81893033333333</v>
       </c>
       <c r="O66">
-        <v>2.480214186666666</v>
+        <v>2.363786066666666</v>
       </c>
       <c r="P66">
-        <v>9.920856746666663</v>
+        <v>9.455144266666665</v>
       </c>
       <c r="Q66">
-        <v>26.22085674666666</v>
+        <v>25.75514426666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1270414449022345</v>
+        <v>0.129170971636238</v>
       </c>
       <c r="T66">
-        <v>1.541120189224214</v>
+        <v>1.581516524459448</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.506398889002048</v>
+        <v>2.340865664224036</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08462584007268331</v>
+        <v>0.08470715998056219</v>
       </c>
       <c r="C67">
-        <v>48.15129782698715</v>
+        <v>46.21441295360231</v>
       </c>
       <c r="D67">
-        <v>158.1462978269871</v>
+        <v>157.9984129536023</v>
       </c>
       <c r="E67">
-        <v>51.18499999999999</v>
+        <v>52.97399999999999</v>
       </c>
       <c r="F67">
-        <v>116.285</v>
+        <v>118.074</v>
       </c>
       <c r="G67">
         <v>6.29</v>
@@ -6769,28 +6769,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M67">
-        <v>8.814402999999999</v>
+        <v>8.9500092</v>
       </c>
       <c r="N67">
-        <v>11.81893033333333</v>
+        <v>11.68332413333333</v>
       </c>
       <c r="O67">
-        <v>2.363786066666666</v>
+        <v>2.336664826666666</v>
       </c>
       <c r="P67">
-        <v>9.455144266666665</v>
+        <v>9.346659306666663</v>
       </c>
       <c r="Q67">
-        <v>25.75514426666667</v>
+        <v>25.64665930666666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.129170971636238</v>
+        <v>0.1314257646487123</v>
       </c>
       <c r="T67">
-        <v>1.581516524459448</v>
+        <v>1.624289114708521</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.340865664224036</v>
+        <v>2.305398002644883</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08470715998056219</v>
+        <v>0.0847884798884411</v>
       </c>
       <c r="C68">
-        <v>46.21441295360231</v>
+        <v>44.27780440036265</v>
       </c>
       <c r="D68">
-        <v>157.9984129536023</v>
+        <v>157.8508044003626</v>
       </c>
       <c r="E68">
-        <v>52.97399999999999</v>
+        <v>54.76299999999999</v>
       </c>
       <c r="F68">
-        <v>118.074</v>
+        <v>119.863</v>
       </c>
       <c r="G68">
         <v>6.29</v>
@@ -6851,28 +6851,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M68">
-        <v>8.9500092</v>
+        <v>9.0856154</v>
       </c>
       <c r="N68">
-        <v>11.68332413333333</v>
+        <v>11.54771793333333</v>
       </c>
       <c r="O68">
-        <v>2.336664826666666</v>
+        <v>2.309543586666666</v>
       </c>
       <c r="P68">
-        <v>9.346659306666663</v>
+        <v>9.238174346666664</v>
       </c>
       <c r="Q68">
-        <v>25.64665930666666</v>
+        <v>25.53817434666666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1314257646487123</v>
+        <v>0.1338172117831548</v>
       </c>
       <c r="T68">
-        <v>1.624289114708521</v>
+        <v>1.669653983154507</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.305398002644883</v>
+        <v>2.270989077232273</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0847884798884411</v>
+        <v>0.08486979979631996</v>
       </c>
       <c r="C69">
-        <v>44.27780440036265</v>
+        <v>42.34147139354255</v>
       </c>
       <c r="D69">
-        <v>157.8508044003626</v>
+        <v>157.7034713935425</v>
       </c>
       <c r="E69">
-        <v>54.76299999999999</v>
+        <v>56.55199999999999</v>
       </c>
       <c r="F69">
-        <v>119.863</v>
+        <v>121.652</v>
       </c>
       <c r="G69">
         <v>6.29</v>
@@ -6933,28 +6933,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M69">
-        <v>9.0856154</v>
+        <v>9.2212216</v>
       </c>
       <c r="N69">
-        <v>11.54771793333333</v>
+        <v>11.41211173333333</v>
       </c>
       <c r="O69">
-        <v>2.309543586666666</v>
+        <v>2.282422346666666</v>
       </c>
       <c r="P69">
-        <v>9.238174346666664</v>
+        <v>9.129689386666664</v>
       </c>
       <c r="Q69">
-        <v>25.53817434666666</v>
+        <v>25.42968938666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1338172117831548</v>
+        <v>0.1363581243634999</v>
       </c>
       <c r="T69">
-        <v>1.669653983154507</v>
+        <v>1.717854155878367</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.270989077232273</v>
+        <v>2.237592179037681</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08486979979631996</v>
+        <v>0.08495111970419886</v>
       </c>
       <c r="C70">
-        <v>42.34147139354255</v>
+        <v>40.40541316230208</v>
       </c>
       <c r="D70">
-        <v>157.7034713935425</v>
+        <v>157.5564131623021</v>
       </c>
       <c r="E70">
-        <v>56.55199999999999</v>
+        <v>58.34099999999999</v>
       </c>
       <c r="F70">
-        <v>121.652</v>
+        <v>123.441</v>
       </c>
       <c r="G70">
         <v>6.29</v>
@@ -7015,28 +7015,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M70">
-        <v>9.2212216</v>
+        <v>9.3568278</v>
       </c>
       <c r="N70">
-        <v>11.41211173333333</v>
+        <v>11.27650553333333</v>
       </c>
       <c r="O70">
-        <v>2.282422346666666</v>
+        <v>2.255301106666666</v>
       </c>
       <c r="P70">
-        <v>9.129689386666664</v>
+        <v>9.021204426666664</v>
       </c>
       <c r="Q70">
-        <v>25.42968938666667</v>
+        <v>25.32120442666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1363581243634999</v>
+        <v>0.1390629667877383</v>
       </c>
       <c r="T70">
-        <v>1.717854155878367</v>
+        <v>1.769164017165056</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.237592179037681</v>
+        <v>2.205163306877715</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08495111970419886</v>
+        <v>0.08503243961207774</v>
       </c>
       <c r="C71">
-        <v>40.40541316230208</v>
+        <v>38.46962893867413</v>
       </c>
       <c r="D71">
-        <v>157.5564131623021</v>
+        <v>157.4096289386741</v>
       </c>
       <c r="E71">
-        <v>58.34099999999999</v>
+        <v>60.13</v>
       </c>
       <c r="F71">
-        <v>123.441</v>
+        <v>125.23</v>
       </c>
       <c r="G71">
         <v>6.29</v>
@@ -7097,28 +7097,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M71">
-        <v>9.3568278</v>
+        <v>9.492433999999999</v>
       </c>
       <c r="N71">
-        <v>11.27650553333333</v>
+        <v>11.14089933333333</v>
       </c>
       <c r="O71">
-        <v>2.255301106666666</v>
+        <v>2.228179866666666</v>
       </c>
       <c r="P71">
-        <v>9.021204426666664</v>
+        <v>8.912719466666664</v>
       </c>
       <c r="Q71">
-        <v>25.32120442666666</v>
+        <v>25.21271946666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1390629667877383</v>
+        <v>0.1419481320402592</v>
       </c>
       <c r="T71">
-        <v>1.769164017165056</v>
+        <v>1.823894535870858</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.205163306877715</v>
+        <v>2.173660973922319</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08503243961207774</v>
+        <v>0.08511375951995664</v>
       </c>
       <c r="C72">
-        <v>38.46962893867413</v>
+        <v>36.53411795755055</v>
       </c>
       <c r="D72">
-        <v>157.4096289386741</v>
+        <v>157.2631179575505</v>
       </c>
       <c r="E72">
-        <v>60.13</v>
+        <v>61.919</v>
       </c>
       <c r="F72">
-        <v>125.23</v>
+        <v>127.019</v>
       </c>
       <c r="G72">
         <v>6.29</v>
@@ -7179,28 +7179,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M72">
-        <v>9.492433999999999</v>
+        <v>9.628040200000001</v>
       </c>
       <c r="N72">
-        <v>11.14089933333333</v>
+        <v>11.00529313333333</v>
       </c>
       <c r="O72">
-        <v>2.228179866666666</v>
+        <v>2.201058626666666</v>
       </c>
       <c r="P72">
-        <v>8.912719466666664</v>
+        <v>8.804234506666663</v>
       </c>
       <c r="Q72">
-        <v>25.21271946666666</v>
+        <v>25.10423450666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1419481320402592</v>
+        <v>0.1450322742067471</v>
       </c>
       <c r="T72">
-        <v>1.823894535870858</v>
+        <v>1.882399573108096</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.173660973922319</v>
+        <v>2.143046030627638</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08511375951995664</v>
+        <v>0.08519507942783552</v>
       </c>
       <c r="C73">
-        <v>36.53411795755056</v>
+        <v>34.59887945666932</v>
       </c>
       <c r="D73">
-        <v>157.2631179575505</v>
+        <v>157.1168794566693</v>
       </c>
       <c r="E73">
-        <v>61.91899999999998</v>
+        <v>63.708</v>
       </c>
       <c r="F73">
-        <v>127.019</v>
+        <v>128.808</v>
       </c>
       <c r="G73">
         <v>6.29</v>
@@ -7261,28 +7261,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M73">
-        <v>9.628040199999999</v>
+        <v>9.763646400000001</v>
       </c>
       <c r="N73">
-        <v>11.00529313333333</v>
+        <v>10.86968693333333</v>
       </c>
       <c r="O73">
-        <v>2.201058626666666</v>
+        <v>2.173937386666666</v>
       </c>
       <c r="P73">
-        <v>8.804234506666663</v>
+        <v>8.695749546666663</v>
       </c>
       <c r="Q73">
-        <v>25.10423450666666</v>
+        <v>24.99574954666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.145032274206747</v>
+        <v>0.1483367122422697</v>
       </c>
       <c r="T73">
-        <v>1.882399573108095</v>
+        <v>1.945083541576563</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.143046030627638</v>
+        <v>2.113281502424476</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08519507942783552</v>
+        <v>0.08527639933571442</v>
       </c>
       <c r="C74">
-        <v>34.59887945666932</v>
+        <v>32.66391267660089</v>
       </c>
       <c r="D74">
-        <v>157.1168794566693</v>
+        <v>156.9709126766009</v>
       </c>
       <c r="E74">
-        <v>63.708</v>
+        <v>65.49699999999999</v>
       </c>
       <c r="F74">
-        <v>128.808</v>
+        <v>130.597</v>
       </c>
       <c r="G74">
         <v>6.29</v>
@@ -7343,28 +7343,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M74">
-        <v>9.763646400000001</v>
+        <v>9.899252599999999</v>
       </c>
       <c r="N74">
-        <v>10.86968693333333</v>
+        <v>10.73408073333333</v>
       </c>
       <c r="O74">
-        <v>2.173937386666666</v>
+        <v>2.146816146666666</v>
       </c>
       <c r="P74">
-        <v>8.695749546666663</v>
+        <v>8.587264586666665</v>
       </c>
       <c r="Q74">
-        <v>24.99574954666667</v>
+        <v>24.88726458666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1483367122422697</v>
+        <v>0.1518859234656089</v>
       </c>
       <c r="T74">
-        <v>1.945083541576563</v>
+        <v>2.012410766968621</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.113281502424476</v>
+        <v>2.084332440747429</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08527639933571442</v>
+        <v>0.08535771924359331</v>
       </c>
       <c r="C75">
-        <v>32.66391267660089</v>
+        <v>30.72921686073525</v>
       </c>
       <c r="D75">
-        <v>156.9709126766009</v>
+        <v>156.8252168607353</v>
       </c>
       <c r="E75">
-        <v>65.49699999999999</v>
+        <v>67.286</v>
       </c>
       <c r="F75">
-        <v>130.597</v>
+        <v>132.386</v>
       </c>
       <c r="G75">
         <v>6.29</v>
@@ -7425,28 +7425,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M75">
-        <v>9.899252599999999</v>
+        <v>10.0348588</v>
       </c>
       <c r="N75">
-        <v>10.73408073333333</v>
+        <v>10.59847453333333</v>
       </c>
       <c r="O75">
-        <v>2.146816146666666</v>
+        <v>2.119694906666666</v>
       </c>
       <c r="P75">
-        <v>8.587264586666665</v>
+        <v>8.478779626666663</v>
       </c>
       <c r="Q75">
-        <v>24.88726458666667</v>
+        <v>24.77877962666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1518859234656089</v>
+        <v>0.1557081509368973</v>
       </c>
       <c r="T75">
-        <v>2.012410766968621</v>
+        <v>2.08491700969853</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.084332440747429</v>
+        <v>2.056165786142734</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08535771924359331</v>
+        <v>0.08543903915147219</v>
       </c>
       <c r="C76">
-        <v>30.72921686073525</v>
+        <v>28.79479125526902</v>
       </c>
       <c r="D76">
-        <v>156.8252168607353</v>
+        <v>156.679791255269</v>
       </c>
       <c r="E76">
-        <v>67.286</v>
+        <v>69.07499999999999</v>
       </c>
       <c r="F76">
-        <v>132.386</v>
+        <v>134.175</v>
       </c>
       <c r="G76">
         <v>6.29</v>
@@ -7507,28 +7507,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M76">
-        <v>10.0348588</v>
+        <v>10.170465</v>
       </c>
       <c r="N76">
-        <v>10.59847453333333</v>
+        <v>10.46286833333333</v>
       </c>
       <c r="O76">
-        <v>2.119694906666666</v>
+        <v>2.092573666666666</v>
       </c>
       <c r="P76">
-        <v>8.478779626666663</v>
+        <v>8.370294666666663</v>
       </c>
       <c r="Q76">
-        <v>24.77877962666666</v>
+        <v>24.67029466666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1557081509368973</v>
+        <v>0.1598361566058888</v>
       </c>
       <c r="T76">
-        <v>2.08491700969853</v>
+        <v>2.163223751846832</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.056165786142734</v>
+        <v>2.028750242327497</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08543903915147219</v>
+        <v>0.08552035905935108</v>
       </c>
       <c r="C77">
-        <v>28.79479125526902</v>
+        <v>26.860635109192</v>
       </c>
       <c r="D77">
-        <v>156.679791255269</v>
+        <v>156.534635109192</v>
       </c>
       <c r="E77">
-        <v>69.07499999999999</v>
+        <v>70.86399999999998</v>
       </c>
       <c r="F77">
-        <v>134.175</v>
+        <v>135.964</v>
       </c>
       <c r="G77">
         <v>6.29</v>
@@ -7589,28 +7589,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M77">
-        <v>10.170465</v>
+        <v>10.3060712</v>
       </c>
       <c r="N77">
-        <v>10.46286833333333</v>
+        <v>10.32726213333333</v>
       </c>
       <c r="O77">
-        <v>2.092573666666666</v>
+        <v>2.065452426666667</v>
       </c>
       <c r="P77">
-        <v>8.370294666666663</v>
+        <v>8.261809706666664</v>
       </c>
       <c r="Q77">
-        <v>24.67029466666666</v>
+        <v>24.56180970666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1598361566058888</v>
+        <v>0.1643081627472961</v>
       </c>
       <c r="T77">
-        <v>2.163223751846832</v>
+        <v>2.248056055840825</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.028750242327497</v>
+        <v>2.00205616019161</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08552035905935108</v>
+        <v>0.09434887896722996</v>
       </c>
       <c r="C78">
-        <v>26.860635109192</v>
+        <v>10.76616519053525</v>
       </c>
       <c r="D78">
-        <v>156.534635109192</v>
+        <v>142.2291651905352</v>
       </c>
       <c r="E78">
-        <v>70.86399999999998</v>
+        <v>72.65299999999999</v>
       </c>
       <c r="F78">
-        <v>135.964</v>
+        <v>137.753</v>
       </c>
       <c r="G78">
         <v>6.29</v>
@@ -7671,45 +7671,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M78">
-        <v>10.3060712</v>
+        <v>12.39777</v>
       </c>
       <c r="N78">
-        <v>10.32726213333333</v>
+        <v>8.235563333333332</v>
       </c>
       <c r="O78">
-        <v>2.065452426666667</v>
+        <v>1.647112666666666</v>
       </c>
       <c r="P78">
-        <v>8.261809706666664</v>
+        <v>6.588450666666665</v>
       </c>
       <c r="Q78">
-        <v>24.56180970666666</v>
+        <v>22.88845066666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1643081627472961</v>
+        <v>0.1691690389879564</v>
       </c>
       <c r="T78">
-        <v>2.248056055840825</v>
+        <v>2.340265081921253</v>
       </c>
       <c r="U78">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.00205616019161</v>
+        <v>1.664277796195068</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09434887896722996</v>
+        <v>0.09454379887510884</v>
       </c>
       <c r="C79">
-        <v>10.76616519053525</v>
+        <v>8.69076504056352</v>
       </c>
       <c r="D79">
-        <v>142.2291651905352</v>
+        <v>141.9427650405635</v>
       </c>
       <c r="E79">
-        <v>72.65299999999999</v>
+        <v>74.44199999999998</v>
       </c>
       <c r="F79">
-        <v>137.753</v>
+        <v>139.542</v>
       </c>
       <c r="G79">
         <v>6.29</v>
@@ -7753,28 +7753,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M79">
-        <v>12.39777</v>
+        <v>12.55878</v>
       </c>
       <c r="N79">
-        <v>8.235563333333332</v>
+        <v>8.074553333333332</v>
       </c>
       <c r="O79">
-        <v>1.647112666666666</v>
+        <v>1.614910666666667</v>
       </c>
       <c r="P79">
-        <v>6.588450666666665</v>
+        <v>6.459642666666666</v>
       </c>
       <c r="Q79">
-        <v>22.88845066666666</v>
+        <v>22.75964266666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1691690389879564</v>
+        <v>0.1744718130686766</v>
       </c>
       <c r="T79">
-        <v>2.340265081921253</v>
+        <v>2.440856746736265</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.664277796195068</v>
+        <v>1.642940901372055</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09454379887510884</v>
+        <v>0.09473871878298776</v>
       </c>
       <c r="C80">
-        <v>8.69076504056352</v>
+        <v>6.616515993570715</v>
       </c>
       <c r="D80">
-        <v>141.9427650405635</v>
+        <v>141.6575159935707</v>
       </c>
       <c r="E80">
-        <v>74.44199999999998</v>
+        <v>76.23099999999999</v>
       </c>
       <c r="F80">
-        <v>139.542</v>
+        <v>141.331</v>
       </c>
       <c r="G80">
         <v>6.29</v>
@@ -7835,28 +7835,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M80">
-        <v>12.55878</v>
+        <v>12.71979</v>
       </c>
       <c r="N80">
-        <v>8.074553333333332</v>
+        <v>7.913543333333331</v>
       </c>
       <c r="O80">
-        <v>1.614910666666667</v>
+        <v>1.582708666666666</v>
       </c>
       <c r="P80">
-        <v>6.459642666666666</v>
+        <v>6.330834666666665</v>
       </c>
       <c r="Q80">
-        <v>22.75964266666666</v>
+        <v>22.63083466666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1744718130686766</v>
+        <v>0.1802796132523226</v>
       </c>
       <c r="T80">
-        <v>2.440856746736265</v>
+        <v>2.551028570105088</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.642940901372055</v>
+        <v>1.622144181101522</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09473871878298776</v>
+        <v>0.09493363869086663</v>
       </c>
       <c r="C81">
-        <v>6.616515993570715</v>
+        <v>4.54341112368445</v>
       </c>
       <c r="D81">
-        <v>141.6575159935707</v>
+        <v>141.3734111236844</v>
       </c>
       <c r="E81">
-        <v>76.23099999999999</v>
+        <v>78.01999999999998</v>
       </c>
       <c r="F81">
-        <v>141.331</v>
+        <v>143.12</v>
       </c>
       <c r="G81">
         <v>6.29</v>
@@ -7917,28 +7917,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M81">
-        <v>12.71979</v>
+        <v>12.8808</v>
       </c>
       <c r="N81">
-        <v>7.913543333333331</v>
+        <v>7.752533333333332</v>
       </c>
       <c r="O81">
-        <v>1.582708666666666</v>
+        <v>1.550506666666666</v>
       </c>
       <c r="P81">
-        <v>6.330834666666665</v>
+        <v>6.202026666666666</v>
       </c>
       <c r="Q81">
-        <v>22.63083466666667</v>
+        <v>22.50202666666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1802796132523226</v>
+        <v>0.1866681934543332</v>
       </c>
       <c r="T81">
-        <v>2.551028570105088</v>
+        <v>2.672217575810793</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.622144181101522</v>
+        <v>1.601867378837754</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09493363869086663</v>
+        <v>0.09512855859874553</v>
       </c>
       <c r="C82">
-        <v>4.54341112368445</v>
+        <v>2.471443560482385</v>
       </c>
       <c r="D82">
-        <v>141.3734111236844</v>
+        <v>141.0904435604824</v>
       </c>
       <c r="E82">
-        <v>78.01999999999998</v>
+        <v>79.809</v>
       </c>
       <c r="F82">
-        <v>143.12</v>
+        <v>144.909</v>
       </c>
       <c r="G82">
         <v>6.29</v>
@@ -7999,28 +7999,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M82">
-        <v>12.8808</v>
+        <v>13.04181</v>
       </c>
       <c r="N82">
-        <v>7.752533333333332</v>
+        <v>7.591523333333331</v>
       </c>
       <c r="O82">
-        <v>1.550506666666666</v>
+        <v>1.518304666666666</v>
       </c>
       <c r="P82">
-        <v>6.202026666666666</v>
+        <v>6.073218666666665</v>
       </c>
       <c r="Q82">
-        <v>22.50202666666667</v>
+        <v>22.37321866666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1866681934543332</v>
+        <v>0.1937292557828712</v>
       </c>
       <c r="T82">
-        <v>2.672217575810793</v>
+        <v>2.806163318959204</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.601867378837754</v>
+        <v>1.582091238358275</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09512855859874553</v>
+        <v>0.09532347850662441</v>
       </c>
       <c r="C83">
-        <v>2.471443560482385</v>
+        <v>0.400606488438882</v>
       </c>
       <c r="D83">
-        <v>141.0904435604824</v>
+        <v>140.8086064884389</v>
       </c>
       <c r="E83">
-        <v>79.809</v>
+        <v>81.59799999999998</v>
       </c>
       <c r="F83">
-        <v>144.909</v>
+        <v>146.698</v>
       </c>
       <c r="G83">
         <v>6.29</v>
@@ -8081,28 +8081,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M83">
-        <v>13.04181</v>
+        <v>13.20282</v>
       </c>
       <c r="N83">
-        <v>7.591523333333331</v>
+        <v>7.430513333333332</v>
       </c>
       <c r="O83">
-        <v>1.518304666666666</v>
+        <v>1.486102666666667</v>
       </c>
       <c r="P83">
-        <v>6.073218666666665</v>
+        <v>5.944410666666665</v>
       </c>
       <c r="Q83">
-        <v>22.37321866666667</v>
+        <v>22.24441066666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1937292557828712</v>
+        <v>0.2015748805923579</v>
       </c>
       <c r="T83">
-        <v>2.806163318959204</v>
+        <v>2.954991922457438</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.582091238358275</v>
+        <v>1.56279744276854</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09532347850662441</v>
+        <v>0.0955183984145033</v>
       </c>
       <c r="C84">
-        <v>0.400606488438882</v>
+        <v>-1.669106853622765</v>
       </c>
       <c r="D84">
-        <v>140.8086064884389</v>
+        <v>140.5278931463772</v>
       </c>
       <c r="E84">
-        <v>81.59799999999998</v>
+        <v>83.387</v>
       </c>
       <c r="F84">
-        <v>146.698</v>
+        <v>148.487</v>
       </c>
       <c r="G84">
         <v>6.29</v>
@@ -8163,28 +8163,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M84">
-        <v>13.20282</v>
+        <v>13.36383</v>
       </c>
       <c r="N84">
-        <v>7.430513333333332</v>
+        <v>7.269503333333331</v>
       </c>
       <c r="O84">
-        <v>1.486102666666667</v>
+        <v>1.453900666666666</v>
       </c>
       <c r="P84">
-        <v>5.944410666666665</v>
+        <v>5.815602666666665</v>
       </c>
       <c r="Q84">
-        <v>22.24441066666667</v>
+        <v>22.11560266666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2015748805923579</v>
+        <v>0.2103435200853136</v>
       </c>
       <c r="T84">
-        <v>2.954991922457438</v>
+        <v>3.121329773426053</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.56279744276854</v>
+        <v>1.543968557915907</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0955183984145033</v>
+        <v>0.09571331832238218</v>
       </c>
       <c r="C85">
-        <v>-1.669106853622765</v>
+        <v>-3.737703173070514</v>
       </c>
       <c r="D85">
-        <v>140.5278931463772</v>
+        <v>140.2482968269295</v>
       </c>
       <c r="E85">
-        <v>83.387</v>
+        <v>85.17599999999999</v>
       </c>
       <c r="F85">
-        <v>148.487</v>
+        <v>150.276</v>
       </c>
       <c r="G85">
         <v>6.29</v>
@@ -8245,28 +8245,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M85">
-        <v>13.36383</v>
+        <v>13.52484</v>
       </c>
       <c r="N85">
-        <v>7.269503333333331</v>
+        <v>7.108493333333332</v>
       </c>
       <c r="O85">
-        <v>1.453900666666666</v>
+        <v>1.421698666666666</v>
       </c>
       <c r="P85">
-        <v>5.815602666666665</v>
+        <v>5.686794666666666</v>
       </c>
       <c r="Q85">
-        <v>22.11560266666667</v>
+        <v>21.98679466666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2103435200853136</v>
+        <v>0.2202082395148888</v>
       </c>
       <c r="T85">
-        <v>3.121329773426053</v>
+        <v>3.308459855765745</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.543968557915907</v>
+        <v>1.525587979845479</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09571331832238218</v>
+        <v>0.09590823823026107</v>
       </c>
       <c r="C86">
-        <v>-3.737703173070514</v>
+        <v>-5.805189123998161</v>
       </c>
       <c r="D86">
-        <v>140.2482968269295</v>
+        <v>139.9698108760018</v>
       </c>
       <c r="E86">
-        <v>85.17599999999999</v>
+        <v>86.96499999999997</v>
       </c>
       <c r="F86">
-        <v>150.276</v>
+        <v>152.065</v>
       </c>
       <c r="G86">
         <v>6.29</v>
@@ -8327,28 +8327,28 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M86">
-        <v>13.52484</v>
+        <v>13.68585</v>
       </c>
       <c r="N86">
-        <v>7.108493333333332</v>
+        <v>6.947483333333333</v>
       </c>
       <c r="O86">
-        <v>1.421698666666666</v>
+        <v>1.389496666666667</v>
       </c>
       <c r="P86">
-        <v>5.686794666666666</v>
+        <v>5.557986666666666</v>
       </c>
       <c r="Q86">
-        <v>21.98679466666667</v>
+        <v>21.85798666666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2202082395148887</v>
+        <v>0.2313882548684072</v>
       </c>
       <c r="T86">
-        <v>3.308459855765742</v>
+        <v>3.520540615750726</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.525587979845479</v>
+        <v>1.507639885964944</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09590823823026107</v>
+        <v>0.1378629612437434</v>
       </c>
       <c r="C87">
-        <v>-5.805189123998161</v>
+        <v>-49.50444238485524</v>
       </c>
       <c r="D87">
-        <v>139.9698108760018</v>
+        <v>98.05955761514474</v>
       </c>
       <c r="E87">
-        <v>86.96499999999997</v>
+        <v>88.75399999999999</v>
       </c>
       <c r="F87">
-        <v>152.065</v>
+        <v>153.854</v>
       </c>
       <c r="G87">
         <v>6.29</v>
@@ -8409,45 +8409,45 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M87">
-        <v>13.68585</v>
+        <v>22.5857672</v>
       </c>
       <c r="N87">
-        <v>6.947483333333333</v>
+        <v>-1.95243386666667</v>
       </c>
       <c r="O87">
-        <v>1.389496666666667</v>
+        <v>-0.390486773333334</v>
       </c>
       <c r="P87">
-        <v>5.557986666666666</v>
+        <v>-1.561947093333336</v>
       </c>
       <c r="Q87">
-        <v>21.85798666666667</v>
+        <v>14.73805290666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2313882548684072</v>
+        <v>0.2477275107071928</v>
       </c>
       <c r="T87">
-        <v>3.520540615750726</v>
+        <v>3.830490261283921</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2</v>
+        <v>0.1827109360565209</v>
       </c>
       <c r="W87">
-        <v>0.07199999999999999</v>
+        <v>0.1199780345869027</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.507639885964944</v>
+        <v>0.9135546802826042</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1378629612437434</v>
+        <v>0.1388729612437433</v>
       </c>
       <c r="C88">
-        <v>-49.50444238485524</v>
+        <v>-51.99521611128725</v>
       </c>
       <c r="D88">
-        <v>98.05955761514474</v>
+        <v>97.35778388871272</v>
       </c>
       <c r="E88">
-        <v>88.75399999999999</v>
+        <v>90.54299999999998</v>
       </c>
       <c r="F88">
-        <v>153.854</v>
+        <v>155.643</v>
       </c>
       <c r="G88">
         <v>6.29</v>
@@ -8491,37 +8491,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M88">
-        <v>22.5857672</v>
+        <v>22.8483924</v>
       </c>
       <c r="N88">
-        <v>-1.95243386666667</v>
+        <v>-2.215059066666669</v>
       </c>
       <c r="O88">
-        <v>-0.390486773333334</v>
+        <v>-0.4430118133333338</v>
       </c>
       <c r="P88">
-        <v>-1.561947093333336</v>
+        <v>-1.772047253333335</v>
       </c>
       <c r="Q88">
-        <v>14.73805290666667</v>
+        <v>14.52795274666667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2477275107071928</v>
+        <v>0.2632603961462077</v>
       </c>
       <c r="T88">
-        <v>3.830490261283921</v>
+        <v>4.125143358305762</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1827109360565209</v>
+        <v>0.1806108103547218</v>
       </c>
       <c r="W88">
-        <v>0.1199780345869027</v>
+        <v>0.1202863330399268</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9135546802826042</v>
+        <v>0.9030540517736089</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1388729612437433</v>
+        <v>0.1398829612437434</v>
       </c>
       <c r="C89">
-        <v>-51.99521611128725</v>
+        <v>-54.4760165747748</v>
       </c>
       <c r="D89">
-        <v>97.35778388871272</v>
+        <v>96.66598342522518</v>
       </c>
       <c r="E89">
-        <v>90.54299999999998</v>
+        <v>92.33199999999999</v>
       </c>
       <c r="F89">
-        <v>155.643</v>
+        <v>157.432</v>
       </c>
       <c r="G89">
         <v>6.29</v>
@@ -8573,37 +8573,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M89">
-        <v>22.8483924</v>
+        <v>23.1110176</v>
       </c>
       <c r="N89">
-        <v>-2.215059066666669</v>
+        <v>-2.477684266666671</v>
       </c>
       <c r="O89">
-        <v>-0.4430118133333338</v>
+        <v>-0.4955368533333342</v>
       </c>
       <c r="P89">
-        <v>-1.772047253333335</v>
+        <v>-1.982147413333337</v>
       </c>
       <c r="Q89">
-        <v>14.52795274666667</v>
+        <v>14.31785258666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2632603961462077</v>
+        <v>0.2813820958250584</v>
       </c>
       <c r="T89">
-        <v>4.125143358305762</v>
+        <v>4.468905304831243</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1806108103547218</v>
+        <v>0.178558414782509</v>
       </c>
       <c r="W89">
-        <v>0.1202863330399268</v>
+        <v>0.1205876247099277</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9030540517736089</v>
+        <v>0.892792073912545</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1398829612437434</v>
+        <v>0.1408929612437434</v>
       </c>
       <c r="C90">
-        <v>-54.4760165747748</v>
+        <v>-56.94705487793406</v>
       </c>
       <c r="D90">
-        <v>96.66598342522518</v>
+        <v>95.9839451220659</v>
       </c>
       <c r="E90">
-        <v>92.33199999999999</v>
+        <v>94.12099999999998</v>
       </c>
       <c r="F90">
-        <v>157.432</v>
+        <v>159.221</v>
       </c>
       <c r="G90">
         <v>6.29</v>
@@ -8655,37 +8655,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M90">
-        <v>23.1110176</v>
+        <v>23.3736428</v>
       </c>
       <c r="N90">
-        <v>-2.477684266666671</v>
+        <v>-2.74030946666667</v>
       </c>
       <c r="O90">
-        <v>-0.4955368533333342</v>
+        <v>-0.548061893333334</v>
       </c>
       <c r="P90">
-        <v>-1.982147413333337</v>
+        <v>-2.192247573333336</v>
       </c>
       <c r="Q90">
-        <v>14.31785258666666</v>
+        <v>14.10775242666666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2813820958250584</v>
+        <v>0.3027986499909728</v>
       </c>
       <c r="T90">
-        <v>4.468905304831243</v>
+        <v>4.875169423452265</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.178558414782509</v>
+        <v>0.1765521404591101</v>
       </c>
       <c r="W90">
-        <v>0.1205876247099277</v>
+        <v>0.1208821457806027</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.892792073912545</v>
+        <v>0.8827607022955501</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1408929612437434</v>
+        <v>0.1419029612437434</v>
       </c>
       <c r="C91">
-        <v>-56.94705487793406</v>
+        <v>-59.40853620728502</v>
       </c>
       <c r="D91">
-        <v>95.9839451220659</v>
+        <v>95.31146379271496</v>
       </c>
       <c r="E91">
-        <v>94.12099999999998</v>
+        <v>95.91</v>
       </c>
       <c r="F91">
-        <v>159.221</v>
+        <v>161.01</v>
       </c>
       <c r="G91">
         <v>6.29</v>
@@ -8737,37 +8737,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M91">
-        <v>23.3736428</v>
+        <v>23.636268</v>
       </c>
       <c r="N91">
-        <v>-2.74030946666667</v>
+        <v>-3.002934666666672</v>
       </c>
       <c r="O91">
-        <v>-0.548061893333334</v>
+        <v>-0.6005869333333345</v>
       </c>
       <c r="P91">
-        <v>-2.192247573333336</v>
+        <v>-2.402347733333337</v>
       </c>
       <c r="Q91">
-        <v>14.10775242666666</v>
+        <v>13.89765226666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3027986499909728</v>
+        <v>0.3284985149900701</v>
       </c>
       <c r="T91">
-        <v>4.875169423452265</v>
+        <v>5.362686365797493</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1765521404591101</v>
+        <v>0.1745904500095644</v>
       </c>
       <c r="W91">
-        <v>0.1208821457806027</v>
+        <v>0.121170121938596</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8827607022955501</v>
+        <v>0.8729522500478217</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1419029612437434</v>
+        <v>0.1429129612437434</v>
       </c>
       <c r="C92">
-        <v>-59.40853620728502</v>
+        <v>-61.86066003905549</v>
       </c>
       <c r="D92">
-        <v>95.31146379271496</v>
+        <v>94.64833996094448</v>
       </c>
       <c r="E92">
-        <v>95.91</v>
+        <v>97.69899999999998</v>
       </c>
       <c r="F92">
-        <v>161.01</v>
+        <v>162.799</v>
       </c>
       <c r="G92">
         <v>6.29</v>
@@ -8819,37 +8819,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M92">
-        <v>23.636268</v>
+        <v>23.8988932</v>
       </c>
       <c r="N92">
-        <v>-3.002934666666672</v>
+        <v>-3.265559866666671</v>
       </c>
       <c r="O92">
-        <v>-0.6005869333333345</v>
+        <v>-0.6531119733333342</v>
       </c>
       <c r="P92">
-        <v>-2.402347733333337</v>
+        <v>-2.612447893333337</v>
       </c>
       <c r="Q92">
-        <v>13.89765226666666</v>
+        <v>13.68755210666666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3284985149900701</v>
+        <v>0.3599094611000779</v>
       </c>
       <c r="T92">
-        <v>5.362686365797493</v>
+        <v>5.958540406441658</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1745904500095644</v>
+        <v>0.1726718736358329</v>
       </c>
       <c r="W92">
-        <v>0.121170121938596</v>
+        <v>0.1214517689502597</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8729522500478217</v>
+        <v>0.8633593681791645</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1429129612437434</v>
+        <v>0.1439229612437434</v>
       </c>
       <c r="C93">
-        <v>-61.86066003905549</v>
+        <v>-64.30362033645413</v>
       </c>
       <c r="D93">
-        <v>94.64833996094448</v>
+        <v>93.99437966354586</v>
       </c>
       <c r="E93">
-        <v>97.69899999999998</v>
+        <v>99.488</v>
       </c>
       <c r="F93">
-        <v>162.799</v>
+        <v>164.588</v>
       </c>
       <c r="G93">
         <v>6.29</v>
@@ -8901,37 +8901,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M93">
-        <v>23.8988932</v>
+        <v>24.1615184</v>
       </c>
       <c r="N93">
-        <v>-3.265559866666671</v>
+        <v>-3.528185066666673</v>
       </c>
       <c r="O93">
-        <v>-0.6531119733333342</v>
+        <v>-0.7056370133333346</v>
       </c>
       <c r="P93">
-        <v>-2.612447893333337</v>
+        <v>-2.822548053333338</v>
       </c>
       <c r="Q93">
-        <v>13.68755210666666</v>
+        <v>13.47745194666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3599094611000779</v>
+        <v>0.3991731437375877</v>
       </c>
       <c r="T93">
-        <v>5.958540406441658</v>
+        <v>6.703357957246867</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1726718736358329</v>
+        <v>0.1707950054441391</v>
       </c>
       <c r="W93">
-        <v>0.1214517689502597</v>
+        <v>0.1217272932008004</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8633593681791645</v>
+        <v>0.8539750272206952</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1439229612437434</v>
+        <v>0.1449329612437434</v>
       </c>
       <c r="C94">
-        <v>-64.30362033645413</v>
+        <v>-66.73760573882055</v>
       </c>
       <c r="D94">
-        <v>93.99437966354586</v>
+        <v>93.34939426117943</v>
       </c>
       <c r="E94">
-        <v>99.488</v>
+        <v>101.277</v>
       </c>
       <c r="F94">
-        <v>164.588</v>
+        <v>166.377</v>
       </c>
       <c r="G94">
         <v>6.29</v>
@@ -8983,37 +8983,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M94">
-        <v>24.1615184</v>
+        <v>24.4241436</v>
       </c>
       <c r="N94">
-        <v>-3.528185066666673</v>
+        <v>-3.790810266666671</v>
       </c>
       <c r="O94">
-        <v>-0.7056370133333346</v>
+        <v>-0.7581620533333343</v>
       </c>
       <c r="P94">
-        <v>-2.822548053333338</v>
+        <v>-3.032648213333337</v>
       </c>
       <c r="Q94">
-        <v>13.47745194666666</v>
+        <v>13.26735178666666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3991731437375877</v>
+        <v>0.449655021414386</v>
       </c>
       <c r="T94">
-        <v>6.703357957246867</v>
+        <v>7.66098052256785</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1707950054441391</v>
+        <v>0.1689585000092558</v>
       </c>
       <c r="W94">
-        <v>0.1217272932008004</v>
+        <v>0.1219968921986413</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8539750272206952</v>
+        <v>0.8447925000462791</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1449329612437434</v>
+        <v>0.1459429612437434</v>
       </c>
       <c r="C95">
-        <v>-66.73760573882055</v>
+        <v>-69.16279974304146</v>
       </c>
       <c r="D95">
-        <v>93.34939426117943</v>
+        <v>92.71320025695853</v>
       </c>
       <c r="E95">
-        <v>101.277</v>
+        <v>103.066</v>
       </c>
       <c r="F95">
-        <v>166.377</v>
+        <v>168.166</v>
       </c>
       <c r="G95">
         <v>6.29</v>
@@ -9065,37 +9065,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M95">
-        <v>24.4241436</v>
+        <v>24.6867688</v>
       </c>
       <c r="N95">
-        <v>-3.790810266666671</v>
+        <v>-4.053435466666674</v>
       </c>
       <c r="O95">
-        <v>-0.7581620533333343</v>
+        <v>-0.8106870933333348</v>
       </c>
       <c r="P95">
-        <v>-3.032648213333337</v>
+        <v>-3.242748373333339</v>
       </c>
       <c r="Q95">
-        <v>13.26735178666666</v>
+        <v>13.05725162666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.449655021414386</v>
+        <v>0.5169641916501171</v>
       </c>
       <c r="T95">
-        <v>7.66098052256785</v>
+        <v>8.937810609662494</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1689585000092558</v>
+        <v>0.1671610691580935</v>
       </c>
       <c r="W95">
-        <v>0.1219968921986413</v>
+        <v>0.1222607550475919</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8447925000462791</v>
+        <v>0.8358053457904676</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1459429612437434</v>
+        <v>0.1469529612437434</v>
       </c>
       <c r="C96">
-        <v>-69.16279974304146</v>
+        <v>-71.57938087759847</v>
       </c>
       <c r="D96">
-        <v>92.71320025695853</v>
+        <v>92.08561912240151</v>
       </c>
       <c r="E96">
-        <v>103.066</v>
+        <v>104.855</v>
       </c>
       <c r="F96">
-        <v>168.166</v>
+        <v>169.955</v>
       </c>
       <c r="G96">
         <v>6.29</v>
@@ -9147,37 +9147,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M96">
-        <v>24.6867688</v>
+        <v>24.949394</v>
       </c>
       <c r="N96">
-        <v>-4.053435466666674</v>
+        <v>-4.316060666666672</v>
       </c>
       <c r="O96">
-        <v>-0.8106870933333348</v>
+        <v>-0.8632121333333345</v>
       </c>
       <c r="P96">
-        <v>-3.242748373333339</v>
+        <v>-3.452848533333338</v>
       </c>
       <c r="Q96">
-        <v>13.05725162666666</v>
+        <v>12.84715146666666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5169641916501171</v>
+        <v>0.6111970299801407</v>
       </c>
       <c r="T96">
-        <v>8.937810609662494</v>
+        <v>10.725372731595</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1671610691580935</v>
+        <v>0.1654014789564294</v>
       </c>
       <c r="W96">
-        <v>0.1222607550475919</v>
+        <v>0.1225190628891962</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8358053457904676</v>
+        <v>0.8270073947821469</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1469529612437434</v>
+        <v>0.1479629612437434</v>
       </c>
       <c r="C97">
-        <v>-71.57938087759847</v>
+        <v>-73.98752286959466</v>
       </c>
       <c r="D97">
-        <v>92.08561912240151</v>
+        <v>91.46647713040534</v>
       </c>
       <c r="E97">
-        <v>104.855</v>
+        <v>106.644</v>
       </c>
       <c r="F97">
-        <v>169.955</v>
+        <v>171.744</v>
       </c>
       <c r="G97">
         <v>6.29</v>
@@ -9229,37 +9229,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M97">
-        <v>24.949394</v>
+        <v>25.2120192</v>
       </c>
       <c r="N97">
-        <v>-4.316060666666672</v>
+        <v>-4.578685866666675</v>
       </c>
       <c r="O97">
-        <v>-0.8632121333333345</v>
+        <v>-0.9157371733333349</v>
       </c>
       <c r="P97">
-        <v>-3.452848533333338</v>
+        <v>-3.66294869333334</v>
       </c>
       <c r="Q97">
-        <v>12.84715146666666</v>
+        <v>12.63705130666666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6111970299801407</v>
+        <v>0.7525462874751763</v>
       </c>
       <c r="T97">
-        <v>10.725372731595</v>
+        <v>13.40671591449375</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1654014789564294</v>
+        <v>0.1636785468839666</v>
       </c>
       <c r="W97">
-        <v>0.1225190628891962</v>
+        <v>0.1227719893174337</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8270073947821469</v>
+        <v>0.8183927344198328</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1479629612437434</v>
+        <v>0.1489729612437434</v>
       </c>
       <c r="C98">
-        <v>-73.98752286959463</v>
+        <v>-76.38739480508794</v>
       </c>
       <c r="D98">
-        <v>91.46647713040534</v>
+        <v>90.85560519491204</v>
       </c>
       <c r="E98">
-        <v>106.644</v>
+        <v>108.433</v>
       </c>
       <c r="F98">
-        <v>171.744</v>
+        <v>173.533</v>
       </c>
       <c r="G98">
         <v>6.29</v>
@@ -9311,37 +9311,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M98">
-        <v>25.2120192</v>
+        <v>25.4746444</v>
       </c>
       <c r="N98">
-        <v>-4.578685866666667</v>
+        <v>-4.84131106666667</v>
       </c>
       <c r="O98">
-        <v>-0.9157371733333335</v>
+        <v>-0.968262213333334</v>
       </c>
       <c r="P98">
-        <v>-3.662948693333334</v>
+        <v>-3.873048853333336</v>
       </c>
       <c r="Q98">
-        <v>12.63705130666667</v>
+        <v>12.42695114666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7525462874751744</v>
+        <v>0.9881283833002326</v>
       </c>
       <c r="T98">
-        <v>13.40671591449371</v>
+        <v>17.87562121932496</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1636785468839666</v>
+        <v>0.1619911391841319</v>
       </c>
       <c r="W98">
-        <v>0.1227719893174337</v>
+        <v>0.1230197007677695</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8183927344198331</v>
+        <v>0.8099556959206594</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1489729612437434</v>
+        <v>0.1499829612437434</v>
       </c>
       <c r="C99">
-        <v>-76.38739480508794</v>
+        <v>-78.77916128304227</v>
       </c>
       <c r="D99">
-        <v>90.85560519491204</v>
+        <v>90.2528387169577</v>
       </c>
       <c r="E99">
-        <v>108.433</v>
+        <v>110.222</v>
       </c>
       <c r="F99">
-        <v>173.533</v>
+        <v>175.322</v>
       </c>
       <c r="G99">
         <v>6.29</v>
@@ -9393,37 +9393,37 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M99">
-        <v>25.4746444</v>
+        <v>25.7372696</v>
       </c>
       <c r="N99">
-        <v>-4.84131106666667</v>
+        <v>-5.103936266666668</v>
       </c>
       <c r="O99">
-        <v>-0.968262213333334</v>
+        <v>-1.020787253333334</v>
       </c>
       <c r="P99">
-        <v>-3.873048853333336</v>
+        <v>-4.083149013333335</v>
       </c>
       <c r="Q99">
-        <v>12.42695114666667</v>
+        <v>12.21685098666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9881283833002326</v>
+        <v>1.459292574950349</v>
       </c>
       <c r="T99">
-        <v>17.87562121932496</v>
+        <v>26.81343182898743</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1619911391841319</v>
+        <v>0.1603381683761306</v>
       </c>
       <c r="W99">
-        <v>0.1230197007677695</v>
+        <v>0.123262356882384</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8099556959206594</v>
+        <v>0.8016908418806528</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1499829612437434</v>
+        <v>0.2058702446417694</v>
       </c>
       <c r="C100">
-        <v>-78.77916128304227</v>
+        <v>-104.8034580450648</v>
       </c>
       <c r="D100">
-        <v>90.2528387169577</v>
+        <v>66.01754195493521</v>
       </c>
       <c r="E100">
-        <v>110.222</v>
+        <v>112.011</v>
       </c>
       <c r="F100">
-        <v>175.322</v>
+        <v>177.111</v>
       </c>
       <c r="G100">
         <v>6.29</v>
@@ -9475,129 +9475,47 @@
         <v>20.63333333333333</v>
       </c>
       <c r="M100">
-        <v>25.7372696</v>
+        <v>35.5638888</v>
       </c>
       <c r="N100">
-        <v>-5.103936266666668</v>
+        <v>-14.93055546666667</v>
       </c>
       <c r="O100">
-        <v>-1.020787253333334</v>
+        <v>-2.986111093333335</v>
       </c>
       <c r="P100">
-        <v>-4.083149013333335</v>
+        <v>-11.94444437333334</v>
       </c>
       <c r="Q100">
-        <v>12.21685098666667</v>
+        <v>4.355555626666664</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.459292574950349</v>
+        <v>3.014513489703297</v>
       </c>
       <c r="T100">
-        <v>26.81343182898743</v>
+        <v>56.31539789216853</v>
       </c>
       <c r="U100">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1603381683761306</v>
+        <v>0.1160353045155924</v>
       </c>
       <c r="W100">
-        <v>0.123262356882384</v>
+        <v>0.1775001108532691</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8016908418806528</v>
+        <v>0.580176522577962</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2058702446417694</v>
-      </c>
-      <c r="C101">
-        <v>-104.8034580450648</v>
-      </c>
-      <c r="D101">
-        <v>66.01754195493521</v>
-      </c>
-      <c r="E101">
-        <v>112.011</v>
-      </c>
-      <c r="F101">
-        <v>177.111</v>
-      </c>
-      <c r="G101">
-        <v>6.29</v>
-      </c>
-      <c r="H101">
-        <v>113.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>36.93333333333333</v>
-      </c>
-      <c r="K101">
-        <v>16.3</v>
-      </c>
-      <c r="L101">
-        <v>20.63333333333333</v>
-      </c>
-      <c r="M101">
-        <v>35.5638888</v>
-      </c>
-      <c r="N101">
-        <v>-14.93055546666667</v>
-      </c>
-      <c r="O101">
-        <v>-2.986111093333335</v>
-      </c>
-      <c r="P101">
-        <v>-11.94444437333334</v>
-      </c>
-      <c r="Q101">
-        <v>4.355555626666664</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.014513489703297</v>
-      </c>
-      <c r="T101">
-        <v>56.31539789216853</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1160353045155924</v>
-      </c>
-      <c r="W101">
-        <v>0.1775001108532691</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.580176522577962</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
